--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E272DCBC-6554-1C48-BA2E-D2634DDCB039}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684BC76D-59BD-674F-BB14-54AF6FDE3258}"/>
   <bookViews>
-    <workbookView xWindow="19100" yWindow="800" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19100" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="852">
   <si>
     <t>ID</t>
   </si>
@@ -3422,6 +3422,22 @@
   </si>
   <si>
     <t>Das Kaffehause</t>
+  </si>
+  <si>
+    <t>Le cinéma comme espace de pouvoir et de destruction
+Dans Prenez garde à la sainte putain, Fassbinder met en scène une équipe de tournage immobilisée dans un hôtel espagnol par des difficultés financières. L'attente, les rivalités et les relations affectives révèlent progressivement les tensions qui traversent le collectif cinématographique.
+L'hôtel devient un espace de surveillance, de désir et de violence, où les rapports professionnels et les relations privées s'entremêlent. Le pouvoir du metteur en scène, incarné par Jeff, repose sur l'autorité, l'humiliation et la menace, mais cette violence révèle aussi son impuissance face aux contraintes économiques et à ses propres dépendances.
+La mise en scène associe le chaos de la production à une forme fragmentée : saynètes discontinues, corps dispersés, dialogues et conflits qui désagrègent le groupe. La séquence finale du film tourné par l'équipe, Patria o Muerte , introduit cependant une rupture : le désordre laisse place à une composition maîtrisée, à des mouvements de caméra élégants et à une temporalité propre au cinéma.
+Le film interroge ainsi la contradiction entre la dimension collective de la création cinématographique et les rapports de domination qui l'organisent. Il met en tension la représentation de la violence et sa reproduction dans les conditions mêmes du tournage. La beauté de l'image finale ne résout pas cette contradiction : elle fait apparaître la puissance formelle du cinéma au sein d'un système de relations destructrices.</t>
+  </si>
+  <si>
+    <t>La fragmentation du sujet dans l'histoire
+À travers l'adaptation du roman d'Alfred Döblin, Fassbinder construit une œuvre télévisuelle où le destin de Franz Biberkopf se trouve pris dans les forces sociales, affectives et historiques du Berlin des années 1920.
+Le collage, caractéristique de l'écriture de Döblin, est transposé au cinéma par la juxtaposition des images, des sons, des textes et des espaces. La ville n'est pas un simple décor : elle constitue un réseau de signes et de forces qui traversent les personnages. Cette forme fragmentée traduit également la difficulté du sujet à se construire comme individu autonome.
+Franz cherche à retrouver une place dans la société après sa sortie de prison, mais son existence reste déterminée par les rapports de pouvoir, la violence et les relations de dépendance. Son corps, notamment après la mutilation infligée par Reinhold, devient le lieu où se manifestent les tensions entre virilité, impuissance, désir et domination.
+Le regard occupe une place centrale dans la mise en scène. Miroirs, surcadrages, obstacles visuels et mouvements de caméra empêchent l'accès direct à une intériorité stable. Les personnages sont constitués par les regards, les fantasmes et les rapports de force qui les entourent.
+L'épilogue radicalise cette fragmentation en faisant éclater les repères narratifs et spatiaux. Le rêve, les références religieuses et mythologiques et les images de violence transforment le récit en une exploration de la culpabilité, du désir et de l'histoire. La trajectoire de Franz ne se conclut pas par une libération définitive : la connaissance de soi reste liée aux forces sociales et historiques qui l'ont constitué.
+Berlin Alexanderplatz interroge ainsi la possibilité de construire une identité individuelle dans un monde traversé par la violence. L'histoire allemande n'est pas seulement un contexte : elle se manifeste dans les corps, les relations et les formes de représentation. L'épilogue fait de la fragmentation du récit une possibilité de connaissance, sans effacer la persistance du passé.</t>
   </si>
 </sst>
 </file>
@@ -3727,9 +3743,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -3770,6 +3783,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3788,343 +3804,6 @@
           <bgColor rgb="FFF3F6F8"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Carlito"/>
-        <scheme val="none"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -4584,6 +4263,343 @@
       </font>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -4597,62 +4613,58 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA46" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA46" dataDxfId="45">
   <tableColumns count="27">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="27"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="22"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="21"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="20"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="19"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="18"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="17"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="14"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="13"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="12"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="11"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="ID" dataDxfId="44"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Titre français" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Titre original" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Année" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Type" dataDxfId="40"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Durée (min)" dataDxfId="39"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Pays" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Réalisation" dataDxfId="37"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Scénario" dataDxfId="36"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Image" dataDxfId="35"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Montage" dataDxfId="34"/>
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Décors" dataDxfId="33"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Musique" dataDxfId="32"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Production" dataDxfId="31"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Distribution artistique" dataDxfId="30"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Équipe technique" dataDxfId="29"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Synopsis" dataDxfId="28"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Extraits" dataDxfId="27"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Analyse" dataDxfId="26"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Bibliographie" dataDxfId="25"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Affiche" dataDxfId="24"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Légende affiche" dataDxfId="23"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Source affiche" dataDxfId="22"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Liens chronologie" dataDxfId="21"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Mots-clés" dataDxfId="20"/>
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Sources" dataDxfId="19"/>
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Statut" dataDxfId="18"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N27" totalsRowShown="0" headerRowDxfId="45" dataDxfId="44">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="ReferentielEntourage" displayName="ReferentielEntourage" ref="A1:N27" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="pers-harry-baer" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Harry Baer" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Baer" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Harry" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Colonne1" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Noyau théâtral / Factory" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Acteur, assistant, production" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Jeu, soutien de production, présence interne" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Proche compagnon de travail et membre du cercle masculin du collectif" dataDxfId="35"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande" dataDxfId="34"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio" dataDxfId="33"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Colonne2" dataDxfId="32"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Témoin de l’intérieur du collectif, relais organisationnel" dataDxfId="31"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Baer.jpg" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="pers-harry-baer" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Harry Baer" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Baer" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Harry" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Colonne1" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Noyau théâtral / Factory" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Acteur, assistant, production" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0100-000008000000}" name="Jeu, soutien de production, présence interne" dataDxfId="8"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0100-000009000000}" name="Proche compagnon de travail et membre du cercle masculin du collectif" dataDxfId="7"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0100-00000A000000}" name="Le Bouc; Les Dieux de la peste; Pourquoi M. R. est-il atteint de folie meurtrière ?; Pionniers à Ingolstadt; Whity; Le Marchand des quatre saisons; Despair; La Troisième génération; Le Secret de Veronika Voss; Lili Marleen; Lola, une femme allemande" dataDxfId="6"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0100-00000B000000}" name="film-1969-le-bouc; film-1970-les-dieux-de-la-peste; film-1970-pourquoi-m-r-est-il-atteint-de-folie-meurtriere; film-1971-pionniers-a-ingolstadt; film-1971-whity; film-1972-le-marchand-des-quatre-saisons; film-1978-despair; film-1979-la-troisieme-generatio" dataDxfId="5"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0100-00000C000000}" name="Colonne2" dataDxfId="4"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0100-00000D000000}" name="Témoin de l’intérieur du collectif, relais organisationnel" dataDxfId="3"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0100-00000E000000}" name="Baer.jpg" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -4808,12 +4820,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="10" style="41" customWidth="1"/>
+    <col min="4" max="4" width="10" style="40" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
@@ -4848,7 +4860,7 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="5" t="s">
@@ -4930,110 +4942,110 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="38" customFormat="1" ht="107" customHeight="1">
-      <c r="A2" s="35" t="s">
+    <row r="2" spans="1:30" s="37" customFormat="1" ht="107" customHeight="1">
+      <c r="A2" s="34" t="s">
         <v>846</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="35" t="s">
         <v>845</v>
       </c>
-      <c r="C2" s="36" t="s">
+      <c r="C2" s="35" t="s">
         <v>845</v>
       </c>
-      <c r="D2" s="36">
+      <c r="D2" s="35">
         <v>1966</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="35"/>
-      <c r="G2" s="36" t="s">
+      <c r="F2" s="34"/>
+      <c r="G2" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="33" t="s">
         <v>34</v>
       </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="35"/>
-      <c r="O2" s="35"/>
-      <c r="P2" s="35"/>
-      <c r="Q2" s="35"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="35"/>
-      <c r="T2" s="35"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="35"/>
-      <c r="W2" s="35"/>
-      <c r="X2" s="35"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="35"/>
-      <c r="AA2" s="35"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
+      <c r="X2" s="34"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="34"/>
+      <c r="AA2" s="34"/>
+      <c r="AB2" s="36"/>
+      <c r="AC2" s="36"/>
+      <c r="AD2" s="36"/>
     </row>
     <row r="3" spans="1:30" s="10" customFormat="1" ht="107" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="C3" s="27" t="s">
         <v>582</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="27">
         <v>1966</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <v>10</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="H3" s="29" t="s">
+      <c r="H3" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J3" s="28" t="s">
+      <c r="J3" s="27" t="s">
         <v>583</v>
       </c>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28" t="s">
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="O3" s="28" t="s">
+      <c r="O3" s="27" t="s">
         <v>585</v>
       </c>
-      <c r="P3" s="28" t="s">
+      <c r="P3" s="27" t="s">
         <v>586</v>
       </c>
-      <c r="Q3" s="28" t="s">
+      <c r="Q3" s="27" t="s">
         <v>587</v>
       </c>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28" t="s">
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="27"/>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27" t="s">
         <v>588</v>
       </c>
-      <c r="AA3" s="28"/>
+      <c r="AA3" s="27"/>
       <c r="AB3" s="1" t="s">
         <v>35</v>
       </c>
@@ -5041,63 +5053,63 @@
       <c r="AD3" s="9"/>
     </row>
     <row r="4" spans="1:30" s="10" customFormat="1" ht="107" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>589</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="27">
         <v>1967</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <v>9</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="27" t="s">
         <v>590</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="L4" s="28"/>
-      <c r="M4" s="28"/>
-      <c r="N4" s="28" t="s">
+      <c r="K4" s="27"/>
+      <c r="L4" s="27"/>
+      <c r="M4" s="27"/>
+      <c r="N4" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="27" t="s">
         <v>591</v>
       </c>
-      <c r="P4" s="28" t="s">
+      <c r="P4" s="27" t="s">
         <v>592</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="27" t="s">
         <v>593</v>
       </c>
-      <c r="R4" s="28"/>
-      <c r="S4" s="28"/>
-      <c r="T4" s="28"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="28" t="s">
+      <c r="R4" s="27"/>
+      <c r="S4" s="27"/>
+      <c r="T4" s="27"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="27" t="s">
         <v>594</v>
       </c>
-      <c r="AA4" s="28"/>
+      <c r="AA4" s="27"/>
       <c r="AB4" s="9" t="s">
         <v>38</v>
       </c>
@@ -5105,71 +5117,71 @@
       <c r="AD4" s="9"/>
     </row>
     <row r="5" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="29" t="s">
+      <c r="C5" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="39">
+      <c r="D5" s="38">
         <v>1969</v>
       </c>
-      <c r="E5" s="29" t="s">
+      <c r="E5" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>88</v>
       </c>
-      <c r="G5" s="29" t="s">
+      <c r="G5" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="29" t="s">
+      <c r="H5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I5" s="29" t="s">
+      <c r="I5" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29" t="s">
+      <c r="J5" s="28"/>
+      <c r="K5" s="28" t="s">
         <v>595</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="28" t="s">
         <v>596</v>
       </c>
-      <c r="M5" s="29" t="s">
+      <c r="M5" s="28" t="s">
         <v>597</v>
       </c>
-      <c r="N5" s="29" t="s">
+      <c r="N5" s="28" t="s">
         <v>598</v>
       </c>
-      <c r="O5" s="29" t="s">
+      <c r="O5" s="28" t="s">
         <v>599</v>
       </c>
-      <c r="P5" s="29" t="s">
+      <c r="P5" s="28" t="s">
         <v>600</v>
       </c>
-      <c r="Q5" s="29" t="s">
+      <c r="Q5" s="28" t="s">
         <v>601</v>
       </c>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29" t="s">
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29" t="s">
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29" t="s">
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28" t="s">
         <v>602</v>
       </c>
-      <c r="AA5" s="29" t="s">
+      <c r="AA5" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB5" s="1" t="s">
@@ -5185,73 +5197,73 @@
       </c>
     </row>
     <row r="6" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="39">
+      <c r="D6" s="38">
         <v>1969</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>88</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29" t="s">
+      <c r="L6" s="28"/>
+      <c r="M6" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="28" t="s">
         <v>603</v>
       </c>
-      <c r="O6" s="29" t="s">
+      <c r="O6" s="28" t="s">
         <v>604</v>
       </c>
-      <c r="P6" s="29" t="s">
+      <c r="P6" s="28" t="s">
         <v>605</v>
       </c>
-      <c r="Q6" s="29" t="s">
+      <c r="Q6" s="28" t="s">
         <v>606</v>
       </c>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29" t="s">
+      <c r="R6" s="28"/>
+      <c r="S6" s="28" t="s">
         <v>842</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29" t="s">
+      <c r="T6" s="28"/>
+      <c r="U6" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29" t="s">
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29" t="s">
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28" t="s">
         <v>607</v>
       </c>
-      <c r="AA6" s="29" t="s">
+      <c r="AA6" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB6" s="1" t="s">
@@ -5267,73 +5279,73 @@
       </c>
     </row>
     <row r="7" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="28" t="s">
         <v>608</v>
       </c>
-      <c r="D7" s="39">
+      <c r="D7" s="38">
         <v>1970</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>91</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="O7" s="29" t="s">
+      <c r="O7" s="28" t="s">
         <v>610</v>
       </c>
-      <c r="P7" s="29" t="s">
+      <c r="P7" s="28" t="s">
         <v>611</v>
       </c>
-      <c r="Q7" s="29" t="s">
+      <c r="Q7" s="28" t="s">
         <v>612</v>
       </c>
-      <c r="R7" s="29"/>
-      <c r="S7" s="29"/>
-      <c r="T7" s="29"/>
-      <c r="U7" s="29" t="s">
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="29"/>
-      <c r="W7" s="29"/>
-      <c r="X7" s="29" t="s">
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="Y7" s="29"/>
-      <c r="Z7" s="29" t="s">
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28" t="s">
         <v>613</v>
       </c>
-      <c r="AA7" s="29" t="s">
+      <c r="AA7" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB7" s="1" t="s">
@@ -5349,71 +5361,71 @@
       </c>
     </row>
     <row r="8" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C8" s="29" t="s">
+      <c r="C8" s="28" t="s">
         <v>614</v>
       </c>
-      <c r="D8" s="39">
+      <c r="D8" s="38">
         <v>1970</v>
       </c>
-      <c r="E8" s="29" t="s">
+      <c r="E8" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>88</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H8" s="29" t="s">
+      <c r="H8" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="I8" s="29" t="s">
+      <c r="I8" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="J8" s="29" t="s">
+      <c r="J8" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N8" s="29" t="s">
+      <c r="N8" s="28" t="s">
         <v>615</v>
       </c>
-      <c r="O8" s="29" t="s">
+      <c r="O8" s="28" t="s">
         <v>616</v>
       </c>
-      <c r="P8" s="29" t="s">
+      <c r="P8" s="28" t="s">
         <v>617</v>
       </c>
-      <c r="Q8" s="29" t="s">
+      <c r="Q8" s="28" t="s">
         <v>618</v>
       </c>
-      <c r="R8" s="29"/>
-      <c r="S8" s="29"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="29"/>
-      <c r="V8" s="29"/>
-      <c r="W8" s="29"/>
-      <c r="X8" s="29" t="s">
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="Y8" s="29"/>
-      <c r="Z8" s="29" t="s">
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28" t="s">
         <v>619</v>
       </c>
-      <c r="AA8" s="29" t="s">
+      <c r="AA8" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB8" s="1" t="s">
@@ -5429,73 +5441,73 @@
       </c>
     </row>
     <row r="9" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="29" t="s">
+      <c r="C9" s="28" t="s">
         <v>620</v>
       </c>
-      <c r="D9" s="39">
+      <c r="D9" s="38">
         <v>1970</v>
       </c>
-      <c r="E9" s="29" t="s">
+      <c r="E9" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>80</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H9" s="29" t="s">
+      <c r="H9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="29" t="s">
+      <c r="I9" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="29" t="s">
+      <c r="J9" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="28" t="s">
         <v>621</v>
       </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N9" s="29" t="s">
+      <c r="N9" s="28" t="s">
         <v>598</v>
       </c>
-      <c r="O9" s="29" t="s">
+      <c r="O9" s="28" t="s">
         <v>622</v>
       </c>
-      <c r="P9" s="29" t="s">
+      <c r="P9" s="28" t="s">
         <v>623</v>
       </c>
-      <c r="Q9" s="29" t="s">
+      <c r="Q9" s="28" t="s">
         <v>624</v>
       </c>
-      <c r="R9" s="29"/>
-      <c r="S9" s="29"/>
-      <c r="T9" s="29"/>
-      <c r="U9" s="29" t="s">
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="V9" s="29"/>
-      <c r="W9" s="29"/>
-      <c r="X9" s="29" t="s">
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="Y9" s="29"/>
-      <c r="Z9" s="29" t="s">
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28" t="s">
         <v>625</v>
       </c>
-      <c r="AA9" s="29" t="s">
+      <c r="AA9" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB9" s="1" t="s">
@@ -5511,69 +5523,69 @@
       </c>
     </row>
     <row r="10" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C10" s="29" t="s">
+      <c r="C10" s="28" t="s">
         <v>626</v>
       </c>
-      <c r="D10" s="39">
+      <c r="D10" s="38">
         <v>1970</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="29">
         <v>90</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="29" t="s">
+      <c r="H10" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="29" t="s">
+      <c r="I10" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="J10" s="29" t="s">
+      <c r="J10" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="L10" s="29" t="s">
+      <c r="L10" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M10" s="29" t="s">
+      <c r="M10" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N10" s="29" t="s">
+      <c r="N10" s="28" t="s">
         <v>628</v>
       </c>
-      <c r="O10" s="29" t="s">
+      <c r="O10" s="28" t="s">
         <v>629</v>
       </c>
-      <c r="P10" s="29" t="s">
+      <c r="P10" s="28" t="s">
         <v>630</v>
       </c>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="29"/>
-      <c r="T10" s="29"/>
-      <c r="U10" s="29"/>
-      <c r="V10" s="29"/>
-      <c r="W10" s="29"/>
-      <c r="X10" s="29" t="s">
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="Y10" s="29"/>
-      <c r="Z10" s="29" t="s">
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28" t="s">
         <v>631</v>
       </c>
-      <c r="AA10" s="29" t="s">
+      <c r="AA10" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB10" s="1" t="s">
@@ -5589,115 +5601,115 @@
       </c>
     </row>
     <row r="11" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>847</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="28" t="s">
         <v>848</v>
       </c>
-      <c r="C11" s="29" t="s">
+      <c r="C11" s="28" t="s">
         <v>849</v>
       </c>
-      <c r="D11" s="39">
+      <c r="D11" s="38">
         <v>1970</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F11" s="30"/>
-      <c r="G11" s="29" t="s">
+      <c r="F11" s="29"/>
+      <c r="G11" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="29" t="s">
+      <c r="H11" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="29"/>
-      <c r="M11" s="29"/>
-      <c r="N11" s="29"/>
-      <c r="O11" s="29"/>
-      <c r="P11" s="29"/>
-      <c r="Q11" s="29"/>
-      <c r="R11" s="29"/>
-      <c r="S11" s="29"/>
-      <c r="T11" s="29"/>
-      <c r="U11" s="29"/>
-      <c r="V11" s="29"/>
-      <c r="W11" s="29"/>
-      <c r="X11" s="29"/>
-      <c r="Y11" s="29"/>
-      <c r="Z11" s="29"/>
-      <c r="AA11" s="29"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+      <c r="K11" s="28"/>
+      <c r="L11" s="28"/>
+      <c r="M11" s="28"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="28"/>
       <c r="AB11" s="1"/>
       <c r="AC11" s="6"/>
       <c r="AD11" s="6"/>
     </row>
     <row r="12" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="39">
+      <c r="C12" s="28"/>
+      <c r="D12" s="38">
         <v>1970</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="E12" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <v>84</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H12" s="29" t="s">
+      <c r="H12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="29" t="s">
+      <c r="I12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="L12" s="29" t="s">
+      <c r="L12" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M12" s="29" t="s">
+      <c r="M12" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N12" s="29" t="s">
+      <c r="N12" s="28" t="s">
         <v>632</v>
       </c>
-      <c r="O12" s="29" t="s">
+      <c r="O12" s="28" t="s">
         <v>633</v>
       </c>
-      <c r="P12" s="29" t="s">
+      <c r="P12" s="28" t="s">
         <v>634</v>
       </c>
-      <c r="Q12" s="29" t="s">
+      <c r="Q12" s="28" t="s">
         <v>635</v>
       </c>
-      <c r="R12" s="29"/>
-      <c r="S12" s="29"/>
-      <c r="T12" s="29"/>
-      <c r="U12" s="29"/>
-      <c r="V12" s="29"/>
-      <c r="W12" s="29"/>
-      <c r="X12" s="29">
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28">
         <v>1970</v>
       </c>
-      <c r="Y12" s="29"/>
-      <c r="Z12" s="29" t="s">
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28" t="s">
         <v>636</v>
       </c>
-      <c r="AA12" s="29"/>
+      <c r="AA12" s="28"/>
       <c r="AB12" s="1" t="s">
         <v>72</v>
       </c>
@@ -5705,69 +5717,69 @@
       <c r="AD12" s="6"/>
     </row>
     <row r="13" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="39">
+      <c r="C13" s="28"/>
+      <c r="D13" s="38">
         <v>1971</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="E13" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="29">
         <v>95</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="G13" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H13" s="29" t="s">
+      <c r="H13" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="29" t="s">
+      <c r="J13" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="28" t="s">
         <v>627</v>
       </c>
-      <c r="L13" s="29" t="s">
+      <c r="L13" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M13" s="29" t="s">
+      <c r="M13" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N13" s="29" t="s">
+      <c r="N13" s="28" t="s">
         <v>637</v>
       </c>
-      <c r="O13" s="29" t="s">
+      <c r="O13" s="28" t="s">
         <v>638</v>
       </c>
-      <c r="P13" s="29" t="s">
+      <c r="P13" s="28" t="s">
         <v>639</v>
       </c>
-      <c r="Q13" s="29" t="s">
+      <c r="Q13" s="28" t="s">
         <v>640</v>
       </c>
-      <c r="R13" s="29"/>
-      <c r="S13" s="29"/>
-      <c r="T13" s="29"/>
-      <c r="U13" s="29"/>
-      <c r="V13" s="29"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29" t="s">
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="Y13" s="29"/>
-      <c r="Z13" s="29" t="s">
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28" t="s">
         <v>641</v>
       </c>
-      <c r="AA13" s="29" t="s">
+      <c r="AA13" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB13" s="1" t="s">
@@ -5783,73 +5795,75 @@
       </c>
     </row>
     <row r="14" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="B14" s="29" t="s">
+      <c r="B14" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="29" t="s">
+      <c r="C14" s="28" t="s">
         <v>642</v>
       </c>
-      <c r="D14" s="39">
+      <c r="D14" s="38">
         <v>1971</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>103</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="29" t="s">
+      <c r="H14" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="29" t="s">
+      <c r="I14" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="J14" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K14" s="28" t="s">
         <v>643</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="L14" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M14" s="29" t="s">
+      <c r="M14" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N14" s="29" t="s">
+      <c r="N14" s="28" t="s">
         <v>644</v>
       </c>
-      <c r="O14" s="29" t="s">
+      <c r="O14" s="28" t="s">
         <v>645</v>
       </c>
-      <c r="P14" s="29" t="s">
+      <c r="P14" s="28" t="s">
         <v>646</v>
       </c>
-      <c r="Q14" s="29" t="s">
+      <c r="Q14" s="28" t="s">
         <v>647</v>
       </c>
-      <c r="R14" s="29"/>
-      <c r="S14" s="29"/>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29" t="s">
+      <c r="R14" s="28"/>
+      <c r="S14" s="28" t="s">
+        <v>850</v>
+      </c>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29" t="s">
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="Y14" s="29"/>
-      <c r="Z14" s="29" t="s">
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28" t="s">
         <v>648</v>
       </c>
-      <c r="AA14" s="29" t="s">
+      <c r="AA14" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB14" s="1" t="s">
@@ -5865,71 +5879,71 @@
       </c>
     </row>
     <row r="15" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="29" t="s">
+      <c r="C15" s="28" t="s">
         <v>649</v>
       </c>
-      <c r="D15" s="39">
+      <c r="D15" s="38">
         <v>1971</v>
       </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <v>84</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="G15" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H15" s="29" t="s">
+      <c r="H15" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="29" t="s">
+      <c r="I15" s="28" t="s">
         <v>650</v>
       </c>
-      <c r="J15" s="29" t="s">
+      <c r="J15" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L15" s="29" t="s">
+      <c r="L15" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M15" s="29" t="s">
+      <c r="M15" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N15" s="29" t="s">
+      <c r="N15" s="28" t="s">
         <v>651</v>
       </c>
-      <c r="O15" s="29" t="s">
+      <c r="O15" s="28" t="s">
         <v>652</v>
       </c>
-      <c r="P15" s="29" t="s">
+      <c r="P15" s="28" t="s">
         <v>653</v>
       </c>
-      <c r="Q15" s="29" t="s">
+      <c r="Q15" s="28" t="s">
         <v>654</v>
       </c>
-      <c r="R15" s="29"/>
-      <c r="S15" s="29"/>
-      <c r="T15" s="29"/>
-      <c r="U15" s="29"/>
-      <c r="V15" s="29"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29" t="s">
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="Y15" s="29"/>
-      <c r="Z15" s="29" t="s">
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28" t="s">
         <v>655</v>
       </c>
-      <c r="AA15" s="29" t="s">
+      <c r="AA15" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB15" s="1" t="s">
@@ -5945,71 +5959,71 @@
       </c>
     </row>
     <row r="16" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A16" s="29" t="s">
+      <c r="A16" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="29" t="s">
+      <c r="C16" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="D16" s="39">
+      <c r="D16" s="38">
         <v>1972</v>
       </c>
-      <c r="E16" s="29" t="s">
+      <c r="E16" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>88</v>
       </c>
-      <c r="G16" s="29" t="s">
+      <c r="G16" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H16" s="29" t="s">
+      <c r="H16" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="29" t="s">
+      <c r="I16" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="29" t="s">
+      <c r="J16" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L16" s="29" t="s">
+      <c r="L16" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29" t="s">
+      <c r="M16" s="28"/>
+      <c r="N16" s="28" t="s">
         <v>656</v>
       </c>
-      <c r="O16" s="29" t="s">
+      <c r="O16" s="28" t="s">
         <v>657</v>
       </c>
-      <c r="P16" s="29" t="s">
+      <c r="P16" s="28" t="s">
         <v>658</v>
       </c>
-      <c r="Q16" s="29" t="s">
+      <c r="Q16" s="28" t="s">
         <v>659</v>
       </c>
-      <c r="R16" s="29"/>
-      <c r="S16" s="29"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="29" t="s">
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="V16" s="29"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29" t="s">
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="Y16" s="29"/>
-      <c r="Z16" s="29" t="s">
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="28" t="s">
         <v>660</v>
       </c>
-      <c r="AA16" s="29" t="s">
+      <c r="AA16" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB16" s="1" t="s">
@@ -6025,71 +6039,71 @@
       </c>
     </row>
     <row r="17" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A17" s="29" t="s">
+      <c r="A17" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="29" t="s">
+      <c r="B17" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="C17" s="29" t="s">
+      <c r="C17" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="D17" s="39">
+      <c r="D17" s="38">
         <v>1972</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="29">
         <v>124</v>
       </c>
-      <c r="G17" s="29" t="s">
+      <c r="G17" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H17" s="29" t="s">
+      <c r="H17" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="29" t="s">
+      <c r="I17" s="28" t="s">
         <v>661</v>
       </c>
-      <c r="J17" s="29" t="s">
+      <c r="J17" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L17" s="29" t="s">
+      <c r="L17" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M17" s="29"/>
-      <c r="N17" s="29" t="s">
+      <c r="M17" s="28"/>
+      <c r="N17" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="O17" s="29" t="s">
+      <c r="O17" s="28" t="s">
         <v>662</v>
       </c>
-      <c r="P17" s="29" t="s">
+      <c r="P17" s="28" t="s">
         <v>663</v>
       </c>
-      <c r="Q17" s="29" t="s">
+      <c r="Q17" s="28" t="s">
         <v>664</v>
       </c>
-      <c r="R17" s="29"/>
-      <c r="S17" s="29"/>
-      <c r="T17" s="29"/>
-      <c r="U17" s="29" t="s">
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="V17" s="29"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29" t="s">
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="Y17" s="29"/>
-      <c r="Z17" s="29" t="s">
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28" t="s">
         <v>665</v>
       </c>
-      <c r="AA17" s="29" t="s">
+      <c r="AA17" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB17" s="1" t="s">
@@ -6105,69 +6119,69 @@
       </c>
     </row>
     <row r="18" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C18" s="28" t="s">
         <v>666</v>
       </c>
-      <c r="D18" s="39">
+      <c r="D18" s="38">
         <v>1972</v>
       </c>
-      <c r="E18" s="29" t="s">
+      <c r="E18" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="29">
         <v>87</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="28" t="s">
         <v>667</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="28" t="s">
         <v>668</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="28" t="s">
         <v>669</v>
       </c>
-      <c r="L18" s="29" t="s">
+      <c r="L18" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M18" s="29"/>
-      <c r="N18" s="29" t="s">
+      <c r="M18" s="28"/>
+      <c r="N18" s="28" t="s">
         <v>670</v>
       </c>
-      <c r="O18" s="29" t="s">
+      <c r="O18" s="28" t="s">
         <v>671</v>
       </c>
-      <c r="P18" s="29" t="s">
+      <c r="P18" s="28" t="s">
         <v>672</v>
       </c>
-      <c r="Q18" s="29" t="s">
+      <c r="Q18" s="28" t="s">
         <v>673</v>
       </c>
-      <c r="R18" s="29"/>
-      <c r="S18" s="29"/>
-      <c r="T18" s="29"/>
-      <c r="U18" s="29"/>
-      <c r="V18" s="29"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29" t="s">
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="Y18" s="29"/>
-      <c r="Z18" s="29" t="s">
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="28" t="s">
         <v>674</v>
       </c>
-      <c r="AA18" s="29" t="s">
+      <c r="AA18" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB18" s="1" t="s">
@@ -6183,71 +6197,71 @@
       </c>
     </row>
     <row r="19" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D19" s="39">
+      <c r="D19" s="38">
         <v>1972</v>
       </c>
-      <c r="E19" s="29" t="s">
+      <c r="E19" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>467</v>
       </c>
-      <c r="G19" s="29" t="s">
+      <c r="G19" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="29" t="s">
+      <c r="H19" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="29" t="s">
+      <c r="I19" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="29" t="s">
+      <c r="J19" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K19" s="29" t="s">
+      <c r="K19" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="L19" s="29" t="s">
+      <c r="L19" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M19" s="29"/>
-      <c r="N19" s="29" t="s">
+      <c r="M19" s="28"/>
+      <c r="N19" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="O19" s="29" t="s">
+      <c r="O19" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="P19" s="29" t="s">
+      <c r="P19" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="Q19" s="29" t="s">
+      <c r="Q19" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="R19" s="29"/>
-      <c r="S19" s="29"/>
-      <c r="T19" s="29"/>
-      <c r="U19" s="29"/>
-      <c r="V19" s="29"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29" t="s">
+      <c r="R19" s="28"/>
+      <c r="S19" s="28"/>
+      <c r="T19" s="28"/>
+      <c r="U19" s="28"/>
+      <c r="V19" s="28"/>
+      <c r="W19" s="28"/>
+      <c r="X19" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="Y19" s="29" t="s">
+      <c r="Y19" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="Z19" s="29" t="s">
+      <c r="Z19" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA19" s="29" t="s">
+      <c r="AA19" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB19" s="1" t="s">
@@ -6263,71 +6277,71 @@
       </c>
     </row>
     <row r="20" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="28" t="s">
         <v>675</v>
       </c>
-      <c r="D20" s="39">
+      <c r="D20" s="38">
         <v>1973</v>
       </c>
-      <c r="E20" s="29" t="s">
+      <c r="E20" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="29">
         <v>102</v>
       </c>
-      <c r="G20" s="29" t="s">
+      <c r="G20" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H20" s="29" t="s">
+      <c r="H20" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I20" s="29" t="s">
+      <c r="I20" s="28" t="s">
         <v>676</v>
       </c>
-      <c r="J20" s="29" t="s">
+      <c r="J20" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="K20" s="29" t="s">
+      <c r="K20" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L20" s="29" t="s">
+      <c r="L20" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M20" s="29" t="s">
+      <c r="M20" s="28" t="s">
         <v>677</v>
       </c>
-      <c r="N20" s="29" t="s">
+      <c r="N20" s="28" t="s">
         <v>678</v>
       </c>
-      <c r="O20" s="29" t="s">
+      <c r="O20" s="28" t="s">
         <v>679</v>
       </c>
-      <c r="P20" s="29" t="s">
+      <c r="P20" s="28" t="s">
         <v>680</v>
       </c>
-      <c r="Q20" s="29" t="s">
+      <c r="Q20" s="28" t="s">
         <v>681</v>
       </c>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29" t="s">
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29" t="s">
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28" t="s">
         <v>682</v>
       </c>
-      <c r="AA20" s="29" t="s">
+      <c r="AA20" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB20" s="1" t="s">
@@ -6343,67 +6357,67 @@
       </c>
     </row>
     <row r="21" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="C21" s="29" t="s">
+      <c r="C21" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="39">
+      <c r="D21" s="38">
         <v>1973</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>212</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G21" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H21" s="29" t="s">
+      <c r="H21" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="29"/>
-      <c r="K21" s="29"/>
-      <c r="L21" s="29"/>
-      <c r="M21" s="29"/>
-      <c r="N21" s="29" t="s">
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="O21" s="29"/>
-      <c r="P21" s="29" t="s">
+      <c r="O21" s="28"/>
+      <c r="P21" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="Q21" s="29" t="s">
+      <c r="Q21" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="R21" s="29"/>
-      <c r="S21" s="29"/>
-      <c r="T21" s="29" t="s">
+      <c r="R21" s="28"/>
+      <c r="S21" s="28"/>
+      <c r="T21" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="U21" s="29" t="s">
+      <c r="U21" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="V21" s="29"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="29" t="s">
+      <c r="V21" s="28"/>
+      <c r="W21" s="28"/>
+      <c r="X21" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="Y21" s="29" t="s">
+      <c r="Y21" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="Z21" s="29" t="s">
+      <c r="Z21" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA21" s="29" t="s">
+      <c r="AA21" s="28" t="s">
         <v>128</v>
       </c>
       <c r="AB21" s="1" t="s">
@@ -6419,65 +6433,65 @@
       </c>
     </row>
     <row r="22" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="38">
         <v>1974</v>
       </c>
-      <c r="E22" s="29" t="s">
+      <c r="E22" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="29">
         <v>93</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G22" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H22" s="29" t="s">
+      <c r="H22" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="29" t="s">
+      <c r="I22" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="L22" s="29"/>
-      <c r="M22" s="29"/>
-      <c r="N22" s="29"/>
-      <c r="O22" s="29" t="s">
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="P22" s="29" t="s">
+      <c r="P22" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="Q22" s="29" t="s">
+      <c r="Q22" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="R22" s="29"/>
-      <c r="S22" s="29"/>
-      <c r="T22" s="29"/>
-      <c r="U22" s="29" t="s">
+      <c r="R22" s="28"/>
+      <c r="S22" s="28"/>
+      <c r="T22" s="28"/>
+      <c r="U22" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="V22" s="29"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29" t="s">
+      <c r="V22" s="28"/>
+      <c r="W22" s="28"/>
+      <c r="X22" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="Y22" s="29" t="s">
+      <c r="Y22" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="Z22" s="29" t="s">
+      <c r="Z22" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA22" s="29" t="s">
+      <c r="AA22" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB22" s="1" t="s">
@@ -6493,75 +6507,75 @@
       </c>
     </row>
     <row r="23" spans="1:30" ht="227.75" customHeight="1">
-      <c r="A23" s="29" t="s">
+      <c r="A23" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="D23" s="39">
+      <c r="D23" s="38">
         <v>1974</v>
       </c>
-      <c r="E23" s="29" t="s">
+      <c r="E23" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="29">
         <v>140</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G23" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H23" s="29" t="s">
+      <c r="H23" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I23" s="29" t="s">
+      <c r="I23" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="J23" s="29" t="s">
+      <c r="J23" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="K23" s="29" t="s">
+      <c r="K23" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L23" s="29" t="s">
+      <c r="L23" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29" t="s">
+      <c r="M23" s="28"/>
+      <c r="N23" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O23" s="29" t="s">
+      <c r="O23" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="P23" s="29" t="s">
+      <c r="P23" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="Q23" s="29" t="s">
+      <c r="Q23" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29" t="s">
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="U23" s="29" t="s">
+      <c r="U23" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29" t="s">
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="Y23" s="29" t="s">
+      <c r="Y23" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="Z23" s="29" t="s">
+      <c r="Z23" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA23" s="29" t="s">
+      <c r="AA23" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB23" s="1" t="s">
@@ -6577,67 +6591,67 @@
       </c>
     </row>
     <row r="24" spans="1:30" ht="133">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="39">
+      <c r="C24" s="28"/>
+      <c r="D24" s="38">
         <v>1974</v>
       </c>
-      <c r="E24" s="29" t="s">
+      <c r="E24" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="29">
         <v>101</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="G24" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H24" s="29" t="s">
+      <c r="H24" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="29" t="s">
+      <c r="I24" s="28" t="s">
         <v>683</v>
       </c>
-      <c r="J24" s="29" t="s">
+      <c r="J24" s="28" t="s">
         <v>684</v>
       </c>
-      <c r="K24" s="29" t="s">
+      <c r="K24" s="28" t="s">
         <v>685</v>
       </c>
-      <c r="L24" s="29" t="s">
+      <c r="L24" s="28" t="s">
         <v>686</v>
       </c>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29" t="s">
+      <c r="M24" s="28"/>
+      <c r="N24" s="28" t="s">
         <v>670</v>
       </c>
-      <c r="O24" s="29" t="s">
+      <c r="O24" s="28" t="s">
         <v>687</v>
       </c>
-      <c r="P24" s="29" t="s">
+      <c r="P24" s="28" t="s">
         <v>688</v>
       </c>
-      <c r="Q24" s="29" t="s">
+      <c r="Q24" s="28" t="s">
         <v>689</v>
       </c>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29" t="s">
+      <c r="R24" s="28"/>
+      <c r="S24" s="28"/>
+      <c r="T24" s="28"/>
+      <c r="U24" s="28"/>
+      <c r="V24" s="28"/>
+      <c r="W24" s="28"/>
+      <c r="X24" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29" t="s">
+      <c r="Y24" s="28"/>
+      <c r="Z24" s="28" t="s">
         <v>690</v>
       </c>
-      <c r="AA24" s="29" t="s">
+      <c r="AA24" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB24" s="1" t="s">
@@ -6652,76 +6666,76 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="228">
-      <c r="A25" s="29" t="s">
+    <row r="25" spans="1:30" ht="247">
+      <c r="A25" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="C25" s="29" t="s">
+      <c r="C25" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="D25" s="39">
+      <c r="D25" s="38">
         <v>1974</v>
       </c>
-      <c r="E25" s="29" t="s">
+      <c r="E25" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="29">
         <v>116</v>
       </c>
-      <c r="G25" s="29" t="s">
+      <c r="G25" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H25" s="29" t="s">
+      <c r="H25" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I25" s="29" t="s">
+      <c r="I25" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="J25" s="29" t="s">
+      <c r="J25" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K25" s="29" t="s">
+      <c r="K25" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="L25" s="29" t="s">
+      <c r="L25" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M25" s="29"/>
-      <c r="N25" s="29" t="s">
+      <c r="M25" s="28"/>
+      <c r="N25" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="O25" s="29" t="s">
+      <c r="O25" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="P25" s="29" t="s">
+      <c r="P25" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="Q25" s="29" t="s">
+      <c r="Q25" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="R25" s="29"/>
-      <c r="S25" s="29" t="s">
+      <c r="R25" s="28"/>
+      <c r="S25" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="T25" s="29" t="s">
+      <c r="T25" s="28" t="s">
         <v>166</v>
       </c>
-      <c r="U25" s="29"/>
-      <c r="V25" s="29"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29" t="s">
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="Y25" s="29" t="s">
+      <c r="Y25" s="28" t="s">
         <v>167</v>
       </c>
-      <c r="Z25" s="29" t="s">
+      <c r="Z25" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA25" s="29" t="s">
+      <c r="AA25" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB25" s="1" t="s">
@@ -6737,75 +6751,75 @@
       </c>
     </row>
     <row r="26" spans="1:30" ht="342">
-      <c r="A26" s="29" t="s">
+      <c r="A26" s="28" t="s">
         <v>169</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="28" t="s">
         <v>170</v>
       </c>
-      <c r="C26" s="29" t="s">
+      <c r="C26" s="28" t="s">
         <v>171</v>
       </c>
-      <c r="D26" s="39">
+      <c r="D26" s="38">
         <v>1975</v>
       </c>
-      <c r="E26" s="29" t="s">
+      <c r="E26" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="29">
         <v>123</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="G26" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H26" s="29" t="s">
+      <c r="H26" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I26" s="29" t="s">
+      <c r="I26" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="J26" s="29" t="s">
+      <c r="J26" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K26" s="29" t="s">
+      <c r="K26" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29" t="s">
+      <c r="L26" s="28"/>
+      <c r="M26" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N26" s="29" t="s">
+      <c r="N26" s="28" t="s">
         <v>174</v>
       </c>
-      <c r="O26" s="29" t="s">
+      <c r="O26" s="28" t="s">
         <v>175</v>
       </c>
-      <c r="P26" s="29" t="s">
+      <c r="P26" s="28" t="s">
         <v>176</v>
       </c>
-      <c r="Q26" s="29" t="s">
+      <c r="Q26" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29" t="s">
+      <c r="R26" s="28"/>
+      <c r="S26" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29" t="s">
+      <c r="T26" s="28"/>
+      <c r="U26" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29" t="s">
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="Y26" s="29" t="s">
+      <c r="Y26" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="Z26" s="29" t="s">
+      <c r="Z26" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA26" s="29" t="s">
+      <c r="AA26" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB26" s="1" t="s">
@@ -6821,79 +6835,79 @@
       </c>
     </row>
     <row r="27" spans="1:30" ht="304">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="B27" s="29" t="s">
+      <c r="B27" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="D27" s="39">
+      <c r="D27" s="38">
         <v>1975</v>
       </c>
-      <c r="E27" s="29" t="s">
+      <c r="E27" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="29">
         <v>120</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H27" s="29" t="s">
+      <c r="H27" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="28" t="s">
         <v>186</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="J27" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K27" s="29" t="s">
+      <c r="K27" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L27" s="29" t="s">
+      <c r="L27" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M27" s="29" t="s">
+      <c r="M27" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N27" s="29" t="s">
+      <c r="N27" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="O27" s="29" t="s">
+      <c r="O27" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="P27" s="29" t="s">
+      <c r="P27" s="28" t="s">
         <v>189</v>
       </c>
-      <c r="Q27" s="29" t="s">
+      <c r="Q27" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29" t="s">
+      <c r="R27" s="28"/>
+      <c r="S27" s="28" t="s">
         <v>191</v>
       </c>
-      <c r="T27" s="29" t="s">
+      <c r="T27" s="28" t="s">
         <v>192</v>
       </c>
-      <c r="U27" s="29" t="s">
+      <c r="U27" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29" t="s">
+      <c r="V27" s="28"/>
+      <c r="W27" s="28"/>
+      <c r="X27" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="Y27" s="29" t="s">
+      <c r="Y27" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="Z27" s="29" t="s">
+      <c r="Z27" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA27" s="29" t="s">
+      <c r="AA27" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB27" s="1" t="s">
@@ -6908,70 +6922,70 @@
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="95">
-      <c r="A28" s="29" t="s">
+    <row r="28" spans="1:30" ht="114">
+      <c r="A28" s="28" t="s">
         <v>196</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="28" t="s">
         <v>197</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>691</v>
       </c>
-      <c r="D28" s="39">
+      <c r="D28" s="38">
         <v>1975</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F28" s="30">
+      <c r="F28" s="29">
         <v>44</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="G28" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="29" t="s">
+      <c r="I28" s="28" t="s">
         <v>692</v>
       </c>
-      <c r="J28" s="29" t="s">
+      <c r="J28" s="28" t="s">
         <v>693</v>
       </c>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29" t="s">
+      <c r="K28" s="28"/>
+      <c r="L28" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>694</v>
       </c>
-      <c r="N28" s="29" t="s">
+      <c r="N28" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="O28" s="29" t="s">
+      <c r="O28" s="28" t="s">
         <v>695</v>
       </c>
-      <c r="P28" s="29" t="s">
+      <c r="P28" s="28" t="s">
         <v>696</v>
       </c>
-      <c r="Q28" s="29" t="s">
+      <c r="Q28" s="28" t="s">
         <v>697</v>
       </c>
-      <c r="R28" s="29"/>
-      <c r="S28" s="29"/>
-      <c r="T28" s="29"/>
-      <c r="U28" s="29"/>
-      <c r="V28" s="29"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29" t="s">
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="Y28" s="29"/>
-      <c r="Z28" s="29" t="s">
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28" t="s">
         <v>698</v>
       </c>
-      <c r="AA28" s="29" t="s">
+      <c r="AA28" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB28" s="1" t="s">
@@ -6987,71 +7001,71 @@
       </c>
     </row>
     <row r="29" spans="1:30" ht="266">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="28" t="s">
         <v>699</v>
       </c>
-      <c r="D29" s="39">
+      <c r="D29" s="38">
         <v>1975</v>
       </c>
-      <c r="E29" s="29" t="s">
+      <c r="E29" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>88</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="G29" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H29" s="29" t="s">
+      <c r="H29" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I29" s="29" t="s">
+      <c r="I29" s="28" t="s">
         <v>700</v>
       </c>
-      <c r="J29" s="29" t="s">
+      <c r="J29" s="28" t="s">
         <v>701</v>
       </c>
-      <c r="K29" s="29" t="s">
+      <c r="K29" s="28" t="s">
         <v>702</v>
       </c>
-      <c r="L29" s="29" t="s">
+      <c r="L29" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M29" s="29" t="s">
+      <c r="M29" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N29" s="29" t="s">
+      <c r="N29" s="28" t="s">
         <v>703</v>
       </c>
-      <c r="O29" s="29" t="s">
+      <c r="O29" s="28" t="s">
         <v>704</v>
       </c>
-      <c r="P29" s="29" t="s">
+      <c r="P29" s="28" t="s">
         <v>705</v>
       </c>
-      <c r="Q29" s="29" t="s">
+      <c r="Q29" s="28" t="s">
         <v>706</v>
       </c>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29" t="s">
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29" t="s">
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28" t="s">
         <v>707</v>
       </c>
-      <c r="AA29" s="29" t="s">
+      <c r="AA29" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB29" s="1" t="s">
@@ -7067,71 +7081,71 @@
       </c>
     </row>
     <row r="30" spans="1:30" ht="190">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="28" t="s">
         <v>203</v>
       </c>
-      <c r="C30" s="29" t="s">
+      <c r="C30" s="28" t="s">
         <v>708</v>
       </c>
-      <c r="D30" s="39">
+      <c r="D30" s="38">
         <v>1976</v>
       </c>
-      <c r="E30" s="29" t="s">
+      <c r="E30" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="29">
         <v>101</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="G30" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H30" s="29" t="s">
+      <c r="H30" s="28" t="s">
         <v>526</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="28" t="s">
         <v>709</v>
       </c>
-      <c r="J30" s="29" t="s">
+      <c r="J30" s="28" t="s">
         <v>710</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29" t="s">
+      <c r="L30" s="28"/>
+      <c r="M30" s="28" t="s">
         <v>711</v>
       </c>
-      <c r="N30" s="29" t="s">
+      <c r="N30" s="28" t="s">
         <v>712</v>
       </c>
-      <c r="O30" s="29" t="s">
+      <c r="O30" s="28" t="s">
         <v>713</v>
       </c>
-      <c r="P30" s="29" t="s">
+      <c r="P30" s="28" t="s">
         <v>714</v>
       </c>
-      <c r="Q30" s="29" t="s">
+      <c r="Q30" s="28" t="s">
         <v>715</v>
       </c>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29" t="s">
+      <c r="R30" s="28"/>
+      <c r="S30" s="28"/>
+      <c r="T30" s="28"/>
+      <c r="U30" s="28" t="s">
         <v>204</v>
       </c>
-      <c r="V30" s="29"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29" t="s">
+      <c r="V30" s="28"/>
+      <c r="W30" s="28"/>
+      <c r="X30" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="Y30" s="29"/>
-      <c r="Z30" s="29" t="s">
+      <c r="Y30" s="28"/>
+      <c r="Z30" s="28" t="s">
         <v>716</v>
       </c>
-      <c r="AA30" s="29" t="s">
+      <c r="AA30" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB30" s="1" t="s">
@@ -7147,77 +7161,77 @@
       </c>
     </row>
     <row r="31" spans="1:30" ht="266">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="28" t="s">
         <v>207</v>
       </c>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="C31" s="29" t="s">
+      <c r="C31" s="28" t="s">
         <v>209</v>
       </c>
-      <c r="D31" s="39">
+      <c r="D31" s="38">
         <v>1976</v>
       </c>
-      <c r="E31" s="29" t="s">
+      <c r="E31" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="29">
         <v>112</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="G31" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H31" s="29" t="s">
+      <c r="H31" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I31" s="29" t="s">
+      <c r="I31" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J31" s="29" t="s">
+      <c r="J31" s="28" t="s">
         <v>210</v>
       </c>
-      <c r="K31" s="29" t="s">
+      <c r="K31" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29" t="s">
+      <c r="L31" s="28"/>
+      <c r="M31" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N31" s="29" t="s">
+      <c r="N31" s="28" t="s">
         <v>211</v>
       </c>
-      <c r="O31" s="29" t="s">
+      <c r="O31" s="28" t="s">
         <v>212</v>
       </c>
-      <c r="P31" s="29" t="s">
+      <c r="P31" s="28" t="s">
         <v>213</v>
       </c>
-      <c r="Q31" s="29" t="s">
+      <c r="Q31" s="28" t="s">
         <v>214</v>
       </c>
-      <c r="R31" s="29"/>
-      <c r="S31" s="29" t="s">
+      <c r="R31" s="28"/>
+      <c r="S31" s="28" t="s">
         <v>215</v>
       </c>
-      <c r="T31" s="29" t="s">
+      <c r="T31" s="28" t="s">
         <v>216</v>
       </c>
-      <c r="U31" s="29" t="s">
+      <c r="U31" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="V31" s="29"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29" t="s">
+      <c r="V31" s="28"/>
+      <c r="W31" s="28"/>
+      <c r="X31" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="Y31" s="29" t="s">
+      <c r="Y31" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="Z31" s="29" t="s">
+      <c r="Z31" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA31" s="29" t="s">
+      <c r="AA31" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB31" s="1" t="s">
@@ -7232,76 +7246,76 @@
         <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="209">
-      <c r="A32" s="29" t="s">
+    <row r="32" spans="1:30" ht="228">
+      <c r="A32" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="C32" s="29" t="s">
+      <c r="C32" s="28" t="s">
         <v>222</v>
       </c>
-      <c r="D32" s="39">
+      <c r="D32" s="38">
         <v>1976</v>
       </c>
-      <c r="E32" s="29" t="s">
+      <c r="E32" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="29">
         <v>96</v>
       </c>
-      <c r="G32" s="29" t="s">
+      <c r="G32" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="H32" s="29" t="s">
+      <c r="H32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I32" s="29" t="s">
+      <c r="I32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J32" s="29" t="s">
+      <c r="J32" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K32" s="29" t="s">
+      <c r="K32" s="28" t="s">
         <v>224</v>
       </c>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29" t="s">
+      <c r="L32" s="28"/>
+      <c r="M32" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N32" s="29" t="s">
+      <c r="N32" s="28" t="s">
         <v>225</v>
       </c>
-      <c r="O32" s="29" t="s">
+      <c r="O32" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="P32" s="29" t="s">
+      <c r="P32" s="28" t="s">
         <v>227</v>
       </c>
-      <c r="Q32" s="29" t="s">
+      <c r="Q32" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29" t="s">
+      <c r="R32" s="28"/>
+      <c r="S32" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29" t="s">
+      <c r="T32" s="28"/>
+      <c r="U32" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29" t="s">
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="Y32" s="29" t="s">
+      <c r="Y32" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="Z32" s="29" t="s">
+      <c r="Z32" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA32" s="29" t="s">
+      <c r="AA32" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB32" s="1" t="s">
@@ -7317,75 +7331,75 @@
       </c>
     </row>
     <row r="33" spans="1:30" ht="409.6">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="28" t="s">
         <v>233</v>
       </c>
-      <c r="B33" s="29" t="s">
+      <c r="B33" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="C33" s="29" t="s">
+      <c r="C33" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="D33" s="39">
+      <c r="D33" s="38">
         <v>1976</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="29">
         <v>104</v>
       </c>
-      <c r="G33" s="29" t="s">
+      <c r="G33" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="29" t="s">
+      <c r="H33" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I33" s="29"/>
-      <c r="J33" s="29" t="s">
+      <c r="I33" s="28"/>
+      <c r="J33" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K33" s="29" t="s">
+      <c r="K33" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="L33" s="29" t="s">
+      <c r="L33" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="M33" s="29" t="s">
+      <c r="M33" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N33" s="29" t="s">
+      <c r="N33" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="O33" s="29" t="s">
+      <c r="O33" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="P33" s="29" t="s">
+      <c r="P33" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="Q33" s="29" t="s">
+      <c r="Q33" s="28" t="s">
         <v>239</v>
       </c>
-      <c r="R33" s="29"/>
-      <c r="S33" s="29" t="s">
+      <c r="R33" s="28"/>
+      <c r="S33" s="28" t="s">
         <v>240</v>
       </c>
-      <c r="T33" s="29"/>
-      <c r="U33" s="29" t="s">
+      <c r="T33" s="28"/>
+      <c r="U33" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="V33" s="29"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29" t="s">
+      <c r="V33" s="28"/>
+      <c r="W33" s="28"/>
+      <c r="X33" s="28" t="s">
         <v>205</v>
       </c>
-      <c r="Y33" s="29" t="s">
+      <c r="Y33" s="28" t="s">
         <v>242</v>
       </c>
-      <c r="Z33" s="29" t="s">
+      <c r="Z33" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA33" s="29" t="s">
+      <c r="AA33" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB33" s="1" t="s">
@@ -7401,67 +7415,67 @@
       </c>
     </row>
     <row r="34" spans="1:30" ht="409.6">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="B34" s="29" t="s">
+      <c r="B34" s="28" t="s">
         <v>245</v>
       </c>
-      <c r="C34" s="29" t="s">
+      <c r="C34" s="28" t="s">
         <v>717</v>
       </c>
-      <c r="D34" s="39">
+      <c r="D34" s="38">
         <v>1977</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F34" s="30">
+      <c r="F34" s="29">
         <v>111</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="G34" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H34" s="29" t="s">
+      <c r="H34" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="28" t="s">
         <v>718</v>
       </c>
-      <c r="J34" s="29" t="s">
+      <c r="J34" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K34" s="29" t="s">
+      <c r="K34" s="28" t="s">
         <v>719</v>
       </c>
-      <c r="L34" s="29" t="s">
+      <c r="L34" s="28" t="s">
         <v>720</v>
       </c>
-      <c r="M34" s="29"/>
-      <c r="N34" s="29"/>
-      <c r="O34" s="29" t="s">
+      <c r="M34" s="28"/>
+      <c r="N34" s="28"/>
+      <c r="O34" s="28" t="s">
         <v>721</v>
       </c>
-      <c r="P34" s="29" t="s">
+      <c r="P34" s="28" t="s">
         <v>722</v>
       </c>
-      <c r="Q34" s="29" t="s">
+      <c r="Q34" s="28" t="s">
         <v>723</v>
       </c>
-      <c r="R34" s="29"/>
-      <c r="S34" s="31"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="29"/>
-      <c r="V34" s="29"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29" t="s">
+      <c r="R34" s="28"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="28"/>
+      <c r="U34" s="28"/>
+      <c r="V34" s="28"/>
+      <c r="W34" s="28"/>
+      <c r="X34" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="Y34" s="29"/>
-      <c r="Z34" s="29" t="s">
+      <c r="Y34" s="28"/>
+      <c r="Z34" s="28" t="s">
         <v>724</v>
       </c>
-      <c r="AA34" s="29" t="s">
+      <c r="AA34" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB34" s="1" t="s">
@@ -7476,68 +7490,68 @@
         <v>pers-michael-ballhaus</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="190">
-      <c r="A35" s="29" t="s">
+    <row r="35" spans="1:30" ht="209">
+      <c r="A35" s="28" t="s">
         <v>248</v>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="28" t="s">
         <v>249</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="28" t="s">
         <v>725</v>
       </c>
-      <c r="D35" s="39">
+      <c r="D35" s="38">
         <v>1977</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="29">
         <v>201</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="G35" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H35" s="29" t="s">
+      <c r="H35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I35" s="29" t="s">
+      <c r="I35" s="28" t="s">
         <v>726</v>
       </c>
-      <c r="J35" s="29" t="s">
+      <c r="J35" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K35" s="29"/>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29" t="s">
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N35" s="29" t="s">
+      <c r="N35" s="28" t="s">
         <v>727</v>
       </c>
-      <c r="O35" s="29" t="s">
+      <c r="O35" s="28" t="s">
         <v>728</v>
       </c>
-      <c r="P35" s="29" t="s">
+      <c r="P35" s="28" t="s">
         <v>729</v>
       </c>
-      <c r="Q35" s="29" t="s">
+      <c r="Q35" s="28" t="s">
         <v>730</v>
       </c>
-      <c r="R35" s="29"/>
-      <c r="S35" s="29"/>
-      <c r="T35" s="29"/>
-      <c r="U35" s="29"/>
-      <c r="V35" s="29"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29" t="s">
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="28" t="s">
         <v>246</v>
       </c>
-      <c r="Y35" s="29"/>
-      <c r="Z35" s="29" t="s">
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28" t="s">
         <v>731</v>
       </c>
-      <c r="AA35" s="29" t="s">
+      <c r="AA35" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB35" s="1" t="s">
@@ -7552,62 +7566,62 @@
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="228">
-      <c r="A36" s="29" t="s">
+    <row r="36" spans="1:30" ht="247">
+      <c r="A36" s="28" t="s">
         <v>251</v>
       </c>
-      <c r="B36" s="29" t="s">
+      <c r="B36" s="28" t="s">
         <v>252</v>
       </c>
-      <c r="C36" s="29"/>
-      <c r="D36" s="39">
+      <c r="C36" s="28"/>
+      <c r="D36" s="38">
         <v>1978</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="29">
         <v>119</v>
       </c>
-      <c r="G36" s="29" t="s">
+      <c r="G36" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H36" s="29" t="s">
+      <c r="H36" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I36" s="29"/>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29"/>
-      <c r="P36" s="29" t="s">
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28" t="s">
         <v>254</v>
       </c>
-      <c r="Q36" s="29" t="s">
+      <c r="Q36" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="R36" s="29"/>
-      <c r="S36" s="29" t="s">
+      <c r="R36" s="28"/>
+      <c r="S36" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="T36" s="29"/>
-      <c r="U36" s="29" t="s">
+      <c r="T36" s="28"/>
+      <c r="U36" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="V36" s="29"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29" t="s">
+      <c r="V36" s="28"/>
+      <c r="W36" s="28"/>
+      <c r="X36" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="Y36" s="29" t="s">
+      <c r="Y36" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="Z36" s="29" t="s">
+      <c r="Z36" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA36" s="29" t="s">
+      <c r="AA36" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB36" s="1" t="s">
@@ -7622,68 +7636,68 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="285">
-      <c r="A37" s="29" t="s">
+    <row r="37" spans="1:30" ht="304">
+      <c r="A37" s="28" t="s">
         <v>261</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="C37" s="29" t="s">
+      <c r="C37" s="28" t="s">
         <v>263</v>
       </c>
-      <c r="D37" s="39">
+      <c r="D37" s="38">
         <v>1978</v>
       </c>
-      <c r="E37" s="29" t="s">
+      <c r="E37" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="29">
         <v>119</v>
       </c>
-      <c r="G37" s="29" t="s">
+      <c r="G37" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="H37" s="29" t="s">
+      <c r="H37" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I37" s="29" t="s">
+      <c r="I37" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29" t="s">
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="P37" s="29" t="s">
+      <c r="P37" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="Q37" s="29" t="s">
+      <c r="Q37" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29" t="s">
+      <c r="R37" s="28"/>
+      <c r="S37" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29" t="s">
+      <c r="T37" s="28"/>
+      <c r="U37" s="28" t="s">
         <v>269</v>
       </c>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29" t="s">
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="Y37" s="29" t="s">
+      <c r="Y37" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="Z37" s="29" t="s">
+      <c r="Z37" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA37" s="29" t="s">
+      <c r="AA37" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB37" s="1" t="s">
@@ -7699,77 +7713,77 @@
       </c>
     </row>
     <row r="38" spans="1:30" ht="409.6">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="B38" s="29" t="s">
+      <c r="B38" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="C38" s="29" t="s">
+      <c r="C38" s="28" t="s">
         <v>732</v>
       </c>
-      <c r="D38" s="39">
+      <c r="D38" s="38">
         <v>1978</v>
       </c>
-      <c r="E38" s="29" t="s">
+      <c r="E38" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="29">
         <v>124</v>
       </c>
-      <c r="G38" s="29" t="s">
+      <c r="G38" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H38" s="29" t="s">
+      <c r="H38" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I38" s="29" t="s">
+      <c r="I38" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J38" s="29" t="s">
+      <c r="J38" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K38" s="29" t="s">
+      <c r="K38" s="28" t="s">
         <v>733</v>
       </c>
-      <c r="L38" s="29"/>
-      <c r="M38" s="29" t="s">
+      <c r="L38" s="28"/>
+      <c r="M38" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N38" s="29" t="s">
+      <c r="N38" s="28" t="s">
         <v>734</v>
       </c>
-      <c r="O38" s="29" t="s">
+      <c r="O38" s="28" t="s">
         <v>735</v>
       </c>
-      <c r="P38" s="29" t="s">
+      <c r="P38" s="28" t="s">
         <v>736</v>
       </c>
-      <c r="Q38" s="29" t="s">
+      <c r="Q38" s="28" t="s">
         <v>737</v>
       </c>
-      <c r="R38" s="29"/>
-      <c r="S38" s="32" t="s">
+      <c r="R38" s="28"/>
+      <c r="S38" s="31" t="s">
         <v>843</v>
       </c>
-      <c r="T38" s="29" t="s">
+      <c r="T38" s="28" t="s">
         <v>841</v>
       </c>
-      <c r="U38" s="29" t="s">
+      <c r="U38" s="28" t="s">
         <v>274</v>
       </c>
-      <c r="V38" s="29"/>
-      <c r="W38" s="29"/>
-      <c r="X38" s="29" t="s">
+      <c r="V38" s="28"/>
+      <c r="W38" s="28"/>
+      <c r="X38" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="Y38" s="29" t="s">
+      <c r="Y38" s="28" t="s">
         <v>738</v>
       </c>
-      <c r="Z38" s="29" t="s">
+      <c r="Z38" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA38" s="29" t="s">
+      <c r="AA38" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB38" s="1" t="s">
@@ -7785,75 +7799,75 @@
       </c>
     </row>
     <row r="39" spans="1:30" ht="409.6">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="29" t="s">
+      <c r="B39" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="C39" s="29" t="s">
+      <c r="C39" s="28" t="s">
         <v>278</v>
       </c>
-      <c r="D39" s="39">
+      <c r="D39" s="38">
         <v>1978</v>
       </c>
-      <c r="E39" s="29" t="s">
+      <c r="E39" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="29">
         <v>120</v>
       </c>
-      <c r="G39" s="29" t="s">
+      <c r="G39" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H39" s="29" t="s">
+      <c r="H39" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I39" s="29" t="s">
+      <c r="I39" s="28" t="s">
         <v>739</v>
       </c>
-      <c r="J39" s="29" t="s">
+      <c r="J39" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29" t="s">
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N39" s="29" t="s">
+      <c r="N39" s="28" t="s">
         <v>740</v>
       </c>
-      <c r="O39" s="29" t="s">
+      <c r="O39" s="28" t="s">
         <v>741</v>
       </c>
-      <c r="P39" s="29" t="s">
+      <c r="P39" s="28" t="s">
         <v>742</v>
       </c>
-      <c r="Q39" s="29" t="s">
+      <c r="Q39" s="28" t="s">
         <v>743</v>
       </c>
-      <c r="R39" s="29"/>
-      <c r="S39" s="29" t="s">
+      <c r="R39" s="28"/>
+      <c r="S39" s="28" t="s">
         <v>744</v>
       </c>
-      <c r="T39" s="29" t="s">
+      <c r="T39" s="28" t="s">
         <v>745</v>
       </c>
-      <c r="U39" s="29" t="s">
+      <c r="U39" s="28" t="s">
         <v>279</v>
       </c>
-      <c r="V39" s="29"/>
-      <c r="W39" s="29"/>
-      <c r="X39" s="33">
+      <c r="V39" s="28"/>
+      <c r="W39" s="28"/>
+      <c r="X39" s="32">
         <v>1978</v>
       </c>
-      <c r="Y39" s="29" t="s">
+      <c r="Y39" s="28" t="s">
         <v>746</v>
       </c>
-      <c r="Z39" s="29" t="s">
+      <c r="Z39" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA39" s="29" t="s">
+      <c r="AA39" s="28" t="s">
         <v>112</v>
       </c>
       <c r="AB39" s="1" t="s">
@@ -7869,71 +7883,71 @@
       </c>
     </row>
     <row r="40" spans="1:30" ht="228">
-      <c r="A40" s="29" t="s">
+      <c r="A40" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="B40" s="29" t="s">
+      <c r="B40" s="28" t="s">
         <v>282</v>
       </c>
-      <c r="C40" s="29" t="s">
+      <c r="C40" s="28" t="s">
         <v>747</v>
       </c>
-      <c r="D40" s="39">
+      <c r="D40" s="38">
         <v>1979</v>
       </c>
-      <c r="E40" s="29" t="s">
+      <c r="E40" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F40" s="30">
+      <c r="F40" s="29">
         <v>105</v>
       </c>
-      <c r="G40" s="29" t="s">
+      <c r="G40" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H40" s="29" t="s">
+      <c r="H40" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I40" s="29" t="s">
+      <c r="I40" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J40" s="29" t="s">
+      <c r="J40" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K40" s="29" t="s">
+      <c r="K40" s="28" t="s">
         <v>478</v>
       </c>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29" t="s">
+      <c r="L40" s="28"/>
+      <c r="M40" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N40" s="29" t="s">
+      <c r="N40" s="28" t="s">
         <v>748</v>
       </c>
-      <c r="O40" s="29" t="s">
+      <c r="O40" s="28" t="s">
         <v>749</v>
       </c>
-      <c r="P40" s="29" t="s">
+      <c r="P40" s="28" t="s">
         <v>750</v>
       </c>
-      <c r="Q40" s="29" t="s">
+      <c r="Q40" s="28" t="s">
         <v>751</v>
       </c>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29" t="s">
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29" t="s">
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28" t="s">
         <v>284</v>
       </c>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29" t="s">
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28" t="s">
         <v>752</v>
       </c>
-      <c r="AA40" s="29" t="s">
+      <c r="AA40" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB40" s="1" t="s">
@@ -7948,72 +7962,74 @@
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="342">
-      <c r="A41" s="29" t="s">
+    <row r="41" spans="1:30" ht="409.6">
+      <c r="A41" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="28" t="s">
         <v>287</v>
       </c>
-      <c r="D41" s="39">
+      <c r="D41" s="38">
         <v>1980</v>
       </c>
-      <c r="E41" s="29" t="s">
+      <c r="E41" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="F41" s="30">
+      <c r="F41" s="29">
         <v>894</v>
       </c>
-      <c r="G41" s="29" t="s">
+      <c r="G41" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H41" s="29" t="s">
+      <c r="H41" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I41" s="29" t="s">
+      <c r="I41" s="28" t="s">
         <v>753</v>
       </c>
-      <c r="J41" s="29" t="s">
+      <c r="J41" s="28" t="s">
         <v>754</v>
       </c>
-      <c r="K41" s="29" t="s">
+      <c r="K41" s="28" t="s">
         <v>478</v>
       </c>
-      <c r="L41" s="29"/>
-      <c r="M41" s="29" t="s">
+      <c r="L41" s="28"/>
+      <c r="M41" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N41" s="29" t="s">
+      <c r="N41" s="28" t="s">
         <v>755</v>
       </c>
-      <c r="O41" s="29" t="s">
+      <c r="O41" s="28" t="s">
         <v>756</v>
       </c>
-      <c r="P41" s="29" t="s">
+      <c r="P41" s="28" t="s">
         <v>757</v>
       </c>
-      <c r="Q41" s="29" t="s">
+      <c r="Q41" s="28" t="s">
         <v>758</v>
       </c>
-      <c r="R41" s="29"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="29"/>
-      <c r="U41" s="29" t="s">
+      <c r="R41" s="28"/>
+      <c r="S41" s="28" t="s">
+        <v>851</v>
+      </c>
+      <c r="T41" s="28"/>
+      <c r="U41" s="28" t="s">
         <v>288</v>
       </c>
-      <c r="V41" s="29"/>
-      <c r="W41" s="29"/>
-      <c r="X41" s="29" t="s">
+      <c r="V41" s="28"/>
+      <c r="W41" s="28"/>
+      <c r="X41" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="Y41" s="29"/>
-      <c r="Z41" s="29" t="s">
+      <c r="Y41" s="28"/>
+      <c r="Z41" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AA41" s="29" t="s">
+      <c r="AA41" s="28" t="s">
         <v>317</v>
       </c>
       <c r="AB41" s="1" t="s">
@@ -8029,73 +8045,73 @@
       </c>
     </row>
     <row r="42" spans="1:30" ht="409.6">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="28" t="s">
         <v>291</v>
       </c>
-      <c r="B42" s="29" t="s">
+      <c r="B42" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="C42" s="29" t="s">
+      <c r="C42" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="D42" s="39">
+      <c r="D42" s="38">
         <v>1981</v>
       </c>
-      <c r="E42" s="29" t="s">
+      <c r="E42" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="29">
         <v>115</v>
       </c>
-      <c r="G42" s="29" t="s">
+      <c r="G42" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H42" s="29" t="s">
+      <c r="H42" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I42" s="29" t="s">
+      <c r="I42" s="28" t="s">
         <v>759</v>
       </c>
-      <c r="J42" s="29" t="s">
+      <c r="J42" s="28" t="s">
         <v>760</v>
       </c>
-      <c r="K42" s="29" t="s">
+      <c r="K42" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="L42" s="29"/>
-      <c r="M42" s="29" t="s">
+      <c r="L42" s="28"/>
+      <c r="M42" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N42" s="29" t="s">
+      <c r="N42" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="O42" s="29" t="s">
+      <c r="O42" s="28" t="s">
         <v>763</v>
       </c>
-      <c r="P42" s="29" t="s">
+      <c r="P42" s="28" t="s">
         <v>764</v>
       </c>
-      <c r="Q42" s="29" t="s">
+      <c r="Q42" s="28" t="s">
         <v>844</v>
       </c>
-      <c r="R42" s="29"/>
-      <c r="S42" s="29" t="s">
+      <c r="R42" s="28"/>
+      <c r="S42" s="28" t="s">
         <v>789</v>
       </c>
-      <c r="T42" s="29"/>
-      <c r="U42" s="29" t="s">
+      <c r="T42" s="28"/>
+      <c r="U42" s="28" t="s">
         <v>293</v>
       </c>
-      <c r="V42" s="29"/>
-      <c r="W42" s="29"/>
-      <c r="X42" s="29" t="s">
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="Y42" s="29"/>
-      <c r="Z42" s="29" t="s">
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28" t="s">
         <v>765</v>
       </c>
-      <c r="AA42" s="29" t="s">
+      <c r="AA42" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB42" s="1" t="s">
@@ -8111,61 +8127,61 @@
       </c>
     </row>
     <row r="43" spans="1:30" ht="76">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="28" t="s">
         <v>296</v>
       </c>
-      <c r="B43" s="29" t="s">
+      <c r="B43" s="28" t="s">
         <v>297</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="28" t="s">
         <v>766</v>
       </c>
-      <c r="D43" s="39">
+      <c r="D43" s="38">
         <v>1981</v>
       </c>
-      <c r="E43" s="29" t="s">
+      <c r="E43" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="29">
         <v>91</v>
       </c>
-      <c r="G43" s="29" t="s">
+      <c r="G43" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H43" s="29" t="s">
+      <c r="H43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="29" t="s">
+      <c r="I43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29" t="s">
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28" t="s">
         <v>767</v>
       </c>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29" t="s">
+      <c r="O43" s="28"/>
+      <c r="P43" s="28" t="s">
         <v>768</v>
       </c>
-      <c r="Q43" s="29" t="s">
+      <c r="Q43" s="28" t="s">
         <v>769</v>
       </c>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29" t="s">
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29" t="s">
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28" t="s">
         <v>770</v>
       </c>
-      <c r="AA43" s="29" t="s">
+      <c r="AA43" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB43" s="1" t="s">
@@ -8180,72 +8196,72 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="304">
-      <c r="A44" s="29" t="s">
+    <row r="44" spans="1:30" ht="323">
+      <c r="A44" s="28" t="s">
         <v>300</v>
       </c>
-      <c r="B44" s="29" t="s">
+      <c r="B44" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="28" t="s">
         <v>771</v>
       </c>
-      <c r="D44" s="39">
+      <c r="D44" s="38">
         <v>1981</v>
       </c>
-      <c r="E44" s="29" t="s">
+      <c r="E44" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="29">
         <v>113</v>
       </c>
-      <c r="G44" s="29" t="s">
+      <c r="G44" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H44" s="29" t="s">
+      <c r="H44" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I44" s="29" t="s">
+      <c r="I44" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="J44" s="29" t="s">
+      <c r="J44" s="28" t="s">
         <v>754</v>
       </c>
-      <c r="K44" s="29" t="s">
+      <c r="K44" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29" t="s">
+      <c r="L44" s="28"/>
+      <c r="M44" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="N44" s="29" t="s">
+      <c r="N44" s="28" t="s">
         <v>774</v>
       </c>
-      <c r="O44" s="29" t="s">
+      <c r="O44" s="28" t="s">
         <v>775</v>
       </c>
-      <c r="P44" s="29" t="s">
+      <c r="P44" s="28" t="s">
         <v>776</v>
       </c>
-      <c r="Q44" s="29" t="s">
+      <c r="Q44" s="28" t="s">
         <v>777</v>
       </c>
-      <c r="R44" s="29"/>
-      <c r="S44" s="29"/>
-      <c r="T44" s="29"/>
-      <c r="U44" s="29" t="s">
+      <c r="R44" s="28"/>
+      <c r="S44" s="28"/>
+      <c r="T44" s="28"/>
+      <c r="U44" s="28" t="s">
         <v>302</v>
       </c>
-      <c r="V44" s="29"/>
-      <c r="W44" s="29"/>
-      <c r="X44" s="29" t="s">
+      <c r="V44" s="28"/>
+      <c r="W44" s="28"/>
+      <c r="X44" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="Y44" s="29"/>
-      <c r="Z44" s="29" t="s">
+      <c r="Y44" s="28"/>
+      <c r="Z44" s="28" t="s">
         <v>778</v>
       </c>
-      <c r="AA44" s="29" t="s">
+      <c r="AA44" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB44" s="1" t="s">
@@ -8260,58 +8276,58 @@
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="380">
-      <c r="A45" s="29" t="s">
+    <row r="45" spans="1:30" ht="398">
+      <c r="A45" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="B45" s="29" t="s">
+      <c r="B45" s="28" t="s">
         <v>305</v>
       </c>
-      <c r="C45" s="29" t="s">
+      <c r="C45" s="28" t="s">
         <v>306</v>
       </c>
-      <c r="D45" s="39">
+      <c r="D45" s="38">
         <v>1981</v>
       </c>
-      <c r="E45" s="29" t="s">
+      <c r="E45" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F45" s="30"/>
-      <c r="G45" s="29" t="s">
+      <c r="F45" s="29"/>
+      <c r="G45" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H45" s="29" t="s">
+      <c r="H45" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29" t="s">
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28" t="s">
         <v>779</v>
       </c>
-      <c r="P45" s="29"/>
-      <c r="Q45" s="29" t="s">
+      <c r="P45" s="28"/>
+      <c r="Q45" s="28" t="s">
         <v>780</v>
       </c>
-      <c r="R45" s="29"/>
-      <c r="S45" s="29"/>
-      <c r="T45" s="29"/>
-      <c r="U45" s="29" t="s">
+      <c r="R45" s="28"/>
+      <c r="S45" s="28"/>
+      <c r="T45" s="28"/>
+      <c r="U45" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="V45" s="29"/>
-      <c r="W45" s="29"/>
-      <c r="X45" s="29" t="s">
+      <c r="V45" s="28"/>
+      <c r="W45" s="28"/>
+      <c r="X45" s="28" t="s">
         <v>294</v>
       </c>
-      <c r="Y45" s="29"/>
-      <c r="Z45" s="29" t="s">
+      <c r="Y45" s="28"/>
+      <c r="Z45" s="28" t="s">
         <v>781</v>
       </c>
-      <c r="AA45" s="29" t="s">
+      <c r="AA45" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB45" s="1" t="s">
@@ -8326,74 +8342,74 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="342">
-      <c r="A46" s="29" t="s">
+    <row r="46" spans="1:30" ht="361">
+      <c r="A46" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="C46" s="29" t="s">
+      <c r="C46" s="28" t="s">
         <v>310</v>
       </c>
-      <c r="D46" s="39">
+      <c r="D46" s="38">
         <v>1982</v>
       </c>
-      <c r="E46" s="29" t="s">
+      <c r="E46" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F46" s="30">
+      <c r="F46" s="29">
         <v>107</v>
       </c>
-      <c r="G46" s="29" t="s">
+      <c r="G46" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="H46" s="29" t="s">
+      <c r="H46" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I46" s="29" t="s">
+      <c r="I46" s="28" t="s">
         <v>782</v>
       </c>
-      <c r="J46" s="29" t="s">
+      <c r="J46" s="28" t="s">
         <v>754</v>
       </c>
-      <c r="K46" s="29" t="s">
+      <c r="K46" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="L46" s="29" t="s">
+      <c r="L46" s="28" t="s">
         <v>783</v>
       </c>
-      <c r="M46" s="29" t="s">
+      <c r="M46" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="N46" s="29" t="s">
+      <c r="N46" s="28" t="s">
         <v>784</v>
       </c>
-      <c r="O46" s="29" t="s">
+      <c r="O46" s="28" t="s">
         <v>785</v>
       </c>
-      <c r="P46" s="29" t="s">
+      <c r="P46" s="28" t="s">
         <v>786</v>
       </c>
-      <c r="Q46" s="29" t="s">
+      <c r="Q46" s="28" t="s">
         <v>787</v>
       </c>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29" t="s">
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28" t="s">
         <v>311</v>
       </c>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29" t="s">
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28" t="s">
         <v>312</v>
       </c>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29" t="s">
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28" t="s">
         <v>788</v>
       </c>
-      <c r="AA46" s="29" t="s">
+      <c r="AA46" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB46" s="1" t="s">
@@ -8409,7 +8425,7 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="V5:AA23 A5:T23">
+  <conditionalFormatting sqref="A5:T23 V5:AA23">
     <cfRule type="expression" dxfId="1" priority="3">
       <formula>MOD(ROW(),2)=0</formula>
     </cfRule>
@@ -8434,12 +8450,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>314</v>
       </c>
@@ -8502,17 +8518,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="107" customHeight="1">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="41" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="27"/>
+      <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:2" ht="133" customHeight="1">
       <c r="A2" s="3" t="s">
@@ -8610,7 +8626,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16">
+    <row r="14" spans="1:2" ht="32">
       <c r="A14" s="4" t="s">
         <v>341</v>
       </c>
@@ -8669,7 +8685,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -9696,7 +9712,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="124">
+    <row r="27" spans="1:14" ht="128">
       <c r="A27" s="26" t="s">
         <v>827</v>
       </c>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{684BC76D-59BD-674F-BB14-54AF6FDE3258}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6F9824-C419-EE40-B461-F25673AA6A54}"/>
   <bookViews>
     <workbookView xWindow="19100" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2753,21 +2753,6 @@
   </si>
   <si>
     <t>Albatros Produktion</t>
-  </si>
-  <si>
-    <t>Hanna Schygulla : Maria Braun
-Klaus Löwitsch : Hermann Braun
-Ivan Desny : Karl Oswald
-Elisabeth Trissenaar : Betti Klenze
-Gottfried John : Willi Klenze
-Hark Bohm : Senkenberg
-George Byrd : Bill
-Gisela Uhlen : la mère
-Peter Berling : Bronski
-Volker Spengler : le chef de train
-Lilo Pempeit : Mme Ehmke
-Karl-Heinz von Hassel : le procureur général
-Rainer Werner Fassbinder : l’homme du marché noir</t>
   </si>
   <si>
     <t>Genre : drame psychologique
@@ -3438,6 +3423,21 @@
 Le regard occupe une place centrale dans la mise en scène. Miroirs, surcadrages, obstacles visuels et mouvements de caméra empêchent l'accès direct à une intériorité stable. Les personnages sont constitués par les regards, les fantasmes et les rapports de force qui les entourent.
 L'épilogue radicalise cette fragmentation en faisant éclater les repères narratifs et spatiaux. Le rêve, les références religieuses et mythologiques et les images de violence transforment le récit en une exploration de la culpabilité, du désir et de l'histoire. La trajectoire de Franz ne se conclut pas par une libération définitive : la connaissance de soi reste liée aux forces sociales et historiques qui l'ont constitué.
 Berlin Alexanderplatz interroge ainsi la possibilité de construire une identité individuelle dans un monde traversé par la violence. L'histoire allemande n'est pas seulement un contexte : elle se manifeste dans les corps, les relations et les formes de représentation. L'épilogue fait de la fragmentation du récit une possibilité de connaissance, sans effacer la persistance du passé.</t>
+  </si>
+  <si>
+    <t>Hanna Schygulla : Maria Braun
+Klaus Löwitsch : Hermann Braun
+Ivan Desny : Karl Oswald
+Elisabeth Trissenaar : Betti Klenze
+John Gottfried : Willi Klenze
+Hark Bohm : Senkenberg
+George Byrd : Bill
+Gisela Uhlen : la mère
+Peter Berling : Bronski
+Volker Spengler : le chef de train
+Lilo Pempeit : Mme Ehmke
+Karl-Heinz von Hassel : le procureur général
+Rainer Werner Fassbinder : l’homme du marché noir</t>
   </si>
 </sst>
 </file>
@@ -4613,6 +4613,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA46" dataDxfId="45">
   <tableColumns count="27">
@@ -4944,13 +4948,13 @@
     </row>
     <row r="2" spans="1:30" s="37" customFormat="1" ht="107" customHeight="1">
       <c r="A2" s="34" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D2" s="35">
         <v>1966</v>
@@ -5248,7 +5252,7 @@
       </c>
       <c r="R6" s="28"/>
       <c r="S6" s="28" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="T6" s="28"/>
       <c r="U6" s="28" t="s">
@@ -5602,13 +5606,13 @@
     </row>
     <row r="11" spans="1:30" ht="227.75" customHeight="1">
       <c r="A11" s="28" t="s">
+        <v>846</v>
+      </c>
+      <c r="B11" s="28" t="s">
         <v>847</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="C11" s="28" t="s">
         <v>848</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>849</v>
       </c>
       <c r="D11" s="38">
         <v>1970</v>
@@ -5848,7 +5852,7 @@
       </c>
       <c r="R14" s="28"/>
       <c r="S14" s="28" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="T14" s="28"/>
       <c r="U14" s="28" t="s">
@@ -7764,10 +7768,10 @@
       </c>
       <c r="R38" s="28"/>
       <c r="S38" s="31" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="T38" s="28" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="U38" s="28" t="s">
         <v>274</v>
@@ -7838,20 +7842,20 @@
         <v>740</v>
       </c>
       <c r="O39" s="28" t="s">
+        <v>851</v>
+      </c>
+      <c r="P39" s="28" t="s">
         <v>741</v>
       </c>
-      <c r="P39" s="28" t="s">
+      <c r="Q39" s="28" t="s">
         <v>742</v>
-      </c>
-      <c r="Q39" s="28" t="s">
-        <v>743</v>
       </c>
       <c r="R39" s="28"/>
       <c r="S39" s="28" t="s">
+        <v>743</v>
+      </c>
+      <c r="T39" s="28" t="s">
         <v>744</v>
-      </c>
-      <c r="T39" s="28" t="s">
-        <v>745</v>
       </c>
       <c r="U39" s="28" t="s">
         <v>279</v>
@@ -7862,7 +7866,7 @@
         <v>1978</v>
       </c>
       <c r="Y39" s="28" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Z39" s="28" t="s">
         <v>111</v>
@@ -7875,7 +7879,7 @@
       </c>
       <c r="AC39" s="6" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
-        <v>pers-hark-bohm; pers-lilo-pempeit; pers-gottfried-john; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
+        <v>pers-hark-bohm; pers-lilo-pempeit; pers-hanna-schygulla; pers-elisabeth-trissenaar</v>
       </c>
       <c r="AD39" s="6" t="str">
         <f>_xlfn.LET(_xlpm.texte,_xlfn.TEXTJOIN(" | ",TRUE,H39:N39,P39),IF(_xlpm.texte="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,_xlpm.texte)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,_xlpm.texte)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,_xlpm.texte)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,_xlpm.texte)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,_xlpm.texte)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,_xlpm.texte)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,_xlpm.texte)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,_xlpm.texte)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,_xlpm.texte)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,_xlpm.texte)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,_xlpm.texte)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,_xlpm.texte)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,_xlpm.texte)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,_xlpm.texte)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,_xlpm.texte)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,_xlpm.texte)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,_xlpm.texte)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,_xlpm.texte)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,_xlpm.texte)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,_xlpm.texte)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,_xlpm.texte)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,_xlpm.texte)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,_xlpm.texte)),'Référentiel entourage'!$A$24,""))))</f>
@@ -7890,7 +7894,7 @@
         <v>282</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D40" s="38">
         <v>1979</v>
@@ -7921,16 +7925,16 @@
         <v>173</v>
       </c>
       <c r="N40" s="28" t="s">
+        <v>747</v>
+      </c>
+      <c r="O40" s="28" t="s">
         <v>748</v>
       </c>
-      <c r="O40" s="28" t="s">
+      <c r="P40" s="28" t="s">
         <v>749</v>
       </c>
-      <c r="P40" s="28" t="s">
+      <c r="Q40" s="28" t="s">
         <v>750</v>
-      </c>
-      <c r="Q40" s="28" t="s">
-        <v>751</v>
       </c>
       <c r="R40" s="28"/>
       <c r="S40" s="28"/>
@@ -7945,7 +7949,7 @@
       </c>
       <c r="Y40" s="28"/>
       <c r="Z40" s="28" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="AA40" s="28" t="s">
         <v>45</v>
@@ -7988,10 +7992,10 @@
         <v>34</v>
       </c>
       <c r="I41" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="J41" s="28" t="s">
         <v>753</v>
-      </c>
-      <c r="J41" s="28" t="s">
-        <v>754</v>
       </c>
       <c r="K41" s="28" t="s">
         <v>478</v>
@@ -8001,20 +8005,20 @@
         <v>173</v>
       </c>
       <c r="N41" s="28" t="s">
+        <v>754</v>
+      </c>
+      <c r="O41" s="28" t="s">
         <v>755</v>
       </c>
-      <c r="O41" s="28" t="s">
+      <c r="P41" s="28" t="s">
         <v>756</v>
       </c>
-      <c r="P41" s="28" t="s">
+      <c r="Q41" s="28" t="s">
         <v>757</v>
-      </c>
-      <c r="Q41" s="28" t="s">
-        <v>758</v>
       </c>
       <c r="R41" s="28"/>
       <c r="S41" s="28" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="T41" s="28"/>
       <c r="U41" s="28" t="s">
@@ -8070,33 +8074,33 @@
         <v>34</v>
       </c>
       <c r="I42" s="28" t="s">
+        <v>758</v>
+      </c>
+      <c r="J42" s="28" t="s">
         <v>759</v>
       </c>
-      <c r="J42" s="28" t="s">
+      <c r="K42" s="28" t="s">
         <v>760</v>
-      </c>
-      <c r="K42" s="28" t="s">
-        <v>761</v>
       </c>
       <c r="L42" s="28"/>
       <c r="M42" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N42" s="28" t="s">
+        <v>761</v>
+      </c>
+      <c r="O42" s="28" t="s">
         <v>762</v>
       </c>
-      <c r="O42" s="28" t="s">
+      <c r="P42" s="28" t="s">
         <v>763</v>
       </c>
-      <c r="P42" s="28" t="s">
-        <v>764</v>
-      </c>
       <c r="Q42" s="28" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="R42" s="28"/>
       <c r="S42" s="28" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="T42" s="28"/>
       <c r="U42" s="28" t="s">
@@ -8109,7 +8113,7 @@
       </c>
       <c r="Y42" s="28"/>
       <c r="Z42" s="28" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="AA42" s="28" t="s">
         <v>45</v>
@@ -8134,7 +8138,7 @@
         <v>297</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D43" s="38">
         <v>1981</v>
@@ -8159,14 +8163,14 @@
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
       <c r="N43" s="28" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O43" s="28"/>
       <c r="P43" s="28" t="s">
+        <v>767</v>
+      </c>
+      <c r="Q43" s="28" t="s">
         <v>768</v>
-      </c>
-      <c r="Q43" s="28" t="s">
-        <v>769</v>
       </c>
       <c r="R43" s="28"/>
       <c r="S43" s="28"/>
@@ -8179,7 +8183,7 @@
       </c>
       <c r="Y43" s="28"/>
       <c r="Z43" s="28" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="AA43" s="28" t="s">
         <v>45</v>
@@ -8204,7 +8208,7 @@
         <v>301</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="D44" s="38">
         <v>1981</v>
@@ -8222,29 +8226,29 @@
         <v>34</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="J44" s="28" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="L44" s="28"/>
       <c r="M44" s="28" t="s">
+        <v>772</v>
+      </c>
+      <c r="N44" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="N44" s="28" t="s">
+      <c r="O44" s="28" t="s">
         <v>774</v>
       </c>
-      <c r="O44" s="28" t="s">
+      <c r="P44" s="28" t="s">
         <v>775</v>
       </c>
-      <c r="P44" s="28" t="s">
+      <c r="Q44" s="28" t="s">
         <v>776</v>
-      </c>
-      <c r="Q44" s="28" t="s">
-        <v>777</v>
       </c>
       <c r="R44" s="28"/>
       <c r="S44" s="28"/>
@@ -8259,7 +8263,7 @@
       </c>
       <c r="Y44" s="28"/>
       <c r="Z44" s="28" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AA44" s="28" t="s">
         <v>45</v>
@@ -8306,11 +8310,11 @@
       <c r="M45" s="28"/>
       <c r="N45" s="28"/>
       <c r="O45" s="28" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="P45" s="28"/>
       <c r="Q45" s="28" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="R45" s="28"/>
       <c r="S45" s="28"/>
@@ -8325,7 +8329,7 @@
       </c>
       <c r="Y45" s="28"/>
       <c r="Z45" s="28" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AA45" s="28" t="s">
         <v>45</v>
@@ -8368,31 +8372,31 @@
         <v>34</v>
       </c>
       <c r="I46" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="J46" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="K46" s="28" t="s">
+        <v>760</v>
+      </c>
+      <c r="L46" s="28" t="s">
         <v>782</v>
-      </c>
-      <c r="J46" s="28" t="s">
-        <v>754</v>
-      </c>
-      <c r="K46" s="28" t="s">
-        <v>761</v>
-      </c>
-      <c r="L46" s="28" t="s">
-        <v>783</v>
       </c>
       <c r="M46" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N46" s="28" t="s">
+        <v>783</v>
+      </c>
+      <c r="O46" s="28" t="s">
         <v>784</v>
       </c>
-      <c r="O46" s="28" t="s">
+      <c r="P46" s="28" t="s">
         <v>785</v>
       </c>
-      <c r="P46" s="28" t="s">
+      <c r="Q46" s="28" t="s">
         <v>786</v>
-      </c>
-      <c r="Q46" s="28" t="s">
-        <v>787</v>
       </c>
       <c r="R46" s="28"/>
       <c r="S46" s="28"/>
@@ -8407,7 +8411,7 @@
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="28" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AA46" s="28" t="s">
         <v>45</v>
@@ -8708,7 +8712,7 @@
         <v>354</v>
       </c>
       <c r="E1" s="12" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F1" s="12" t="s">
         <v>355</v>
@@ -8726,10 +8730,10 @@
         <v>359</v>
       </c>
       <c r="K1" s="13" t="s">
+        <v>838</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>839</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>840</v>
       </c>
       <c r="M1" s="14" t="s">
         <v>360</v>
@@ -8860,42 +8864,42 @@
     </row>
     <row r="5" spans="1:14" ht="182">
       <c r="A5" s="15" t="s">
+        <v>789</v>
+      </c>
+      <c r="B5" s="16" t="s">
         <v>790</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="C5" s="16" t="s">
         <v>791</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>792</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>793</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="G5" s="16" t="s">
         <v>389</v>
       </c>
       <c r="H5" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>795</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="J5" s="16" t="s">
         <v>796</v>
       </c>
-      <c r="J5" s="16" t="s">
+      <c r="K5" s="17" t="s">
         <v>797</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>798</v>
       </c>
       <c r="L5" s="16"/>
       <c r="M5" s="14" t="s">
+        <v>798</v>
+      </c>
+      <c r="N5" s="16" t="s">
         <v>799</v>
-      </c>
-      <c r="N5" s="16" t="s">
-        <v>800</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="84">
@@ -8953,7 +8957,7 @@
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G7" s="16" t="s">
         <v>412</v>
@@ -9058,13 +9062,13 @@
     </row>
     <row r="10" spans="1:14" ht="144">
       <c r="A10" s="15" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B10" s="16" t="s">
         <v>590</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>364</v>
@@ -9074,26 +9078,26 @@
         <v>355</v>
       </c>
       <c r="G10" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="H10" s="16" t="s">
         <v>804</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="I10" s="16" t="s">
         <v>805</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="J10" s="16" t="s">
         <v>806</v>
       </c>
-      <c r="J10" s="16" t="s">
+      <c r="K10" s="19" t="s">
         <v>807</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>808</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="14" t="s">
+        <v>808</v>
+      </c>
+      <c r="N10" s="16" t="s">
         <v>809</v>
-      </c>
-      <c r="N10" s="16" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="108">
@@ -9143,7 +9147,7 @@
         <v>452</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
@@ -9274,7 +9278,7 @@
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="14" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="N15" s="16" t="s">
         <v>486</v>
@@ -9394,7 +9398,7 @@
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="14" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="N18" s="16" t="s">
         <v>516</v>
@@ -9503,10 +9507,10 @@
         <v>541</v>
       </c>
       <c r="J21" s="16" t="s">
+        <v>813</v>
+      </c>
+      <c r="K21" s="17" t="s">
         <v>814</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>815</v>
       </c>
       <c r="L21" s="16" t="s">
         <v>542</v>
@@ -9560,16 +9564,16 @@
     </row>
     <row r="23" spans="1:14" ht="168">
       <c r="A23" s="21" t="s">
+        <v>815</v>
+      </c>
+      <c r="B23" s="16" t="s">
         <v>816</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="C23" s="16" t="s">
         <v>817</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="D23" s="16" t="s">
         <v>818</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>819</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="16" t="s">
@@ -9579,23 +9583,23 @@
         <v>401</v>
       </c>
       <c r="H23" s="16" t="s">
+        <v>819</v>
+      </c>
+      <c r="I23" s="16" t="s">
         <v>820</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="J23" s="22" t="s">
         <v>821</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="K23" s="17" t="s">
         <v>822</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>823</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="14" t="s">
+        <v>823</v>
+      </c>
+      <c r="N23" s="16" t="s">
         <v>824</v>
-      </c>
-      <c r="N23" s="16" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="42">
@@ -9706,7 +9710,7 @@
       </c>
       <c r="L26" s="24"/>
       <c r="M26" s="14" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="N26" s="24" t="s">
         <v>581</v>
@@ -9714,42 +9718,42 @@
     </row>
     <row r="27" spans="1:14" ht="128">
       <c r="A27" s="26" t="s">
+        <v>826</v>
+      </c>
+      <c r="B27" s="26" t="s">
         <v>827</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="C27" s="26" t="s">
         <v>828</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="D27" s="26" t="s">
         <v>829</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>830</v>
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="26" t="s">
         <v>529</v>
       </c>
       <c r="G27" s="26" t="s">
+        <v>830</v>
+      </c>
+      <c r="H27" s="26" t="s">
         <v>831</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="I27" s="8" t="s">
         <v>832</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="J27" s="26" t="s">
         <v>833</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="K27" s="8" t="s">
         <v>834</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>835</v>
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="8" t="s">
+        <v>835</v>
+      </c>
+      <c r="N27" s="26" t="s">
         <v>836</v>
-      </c>
-      <c r="N27" s="26" t="s">
-        <v>837</v>
       </c>
     </row>
   </sheetData>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6F9824-C419-EE40-B461-F25673AA6A54}"/>
+  <xr:revisionPtr revIDLastSave="63" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B33C91-36F2-DE40-9621-665068ED7DF4}"/>
   <bookViews>
     <workbookView xWindow="19100" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="852">
   <si>
     <t>ID</t>
   </si>
@@ -4613,10 +4613,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="FilmsTable" displayName="FilmsTable" ref="A1:AA46" dataDxfId="45">
   <tableColumns count="27">
@@ -4824,7 +4820,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AD46"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
@@ -6670,7 +6666,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="247">
+    <row r="25" spans="1:30" ht="228">
       <c r="A25" s="28" t="s">
         <v>156</v>
       </c>
@@ -6926,7 +6922,7 @@
         <v>pers-michael-ballhaus; pers-kurt-raab; pers-peer-raben</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="114">
+    <row r="28" spans="1:30" ht="95">
       <c r="A28" s="28" t="s">
         <v>196</v>
       </c>
@@ -7250,7 +7246,7 @@
         <v>pers-michael-ballhaus; pers-michael-fengler; pers-peer-raben</v>
       </c>
     </row>
-    <row r="32" spans="1:30" ht="228">
+    <row r="32" spans="1:30" ht="209">
       <c r="A32" s="28" t="s">
         <v>220</v>
       </c>
@@ -7494,7 +7490,7 @@
         <v>pers-michael-ballhaus</v>
       </c>
     </row>
-    <row r="35" spans="1:30" ht="209">
+    <row r="35" spans="1:30" ht="190">
       <c r="A35" s="28" t="s">
         <v>248</v>
       </c>
@@ -7570,7 +7566,7 @@
         <v>pers-michael-ballhaus; pers-peer-raben</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="247">
+    <row r="36" spans="1:30" ht="228">
       <c r="A36" s="28" t="s">
         <v>251</v>
       </c>
@@ -7640,7 +7636,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:30" ht="304">
+    <row r="37" spans="1:30" ht="285">
       <c r="A37" s="28" t="s">
         <v>261</v>
       </c>
@@ -7862,8 +7858,8 @@
       </c>
       <c r="V39" s="28"/>
       <c r="W39" s="28"/>
-      <c r="X39" s="32">
-        <v>1978</v>
+      <c r="X39" s="32" t="s">
+        <v>284</v>
       </c>
       <c r="Y39" s="28" t="s">
         <v>745</v>
@@ -8200,7 +8196,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:30" ht="323">
+    <row r="44" spans="1:30" ht="304">
       <c r="A44" s="28" t="s">
         <v>300</v>
       </c>
@@ -8280,7 +8276,7 @@
         <v>pers-juliane-lorenz; pers-peer-raben</v>
       </c>
     </row>
-    <row r="45" spans="1:30" ht="398">
+    <row r="45" spans="1:30" ht="380">
       <c r="A45" s="28" t="s">
         <v>304</v>
       </c>
@@ -8346,7 +8342,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:30" ht="361">
+    <row r="46" spans="1:30" ht="342">
       <c r="A46" s="28" t="s">
         <v>309</v>
       </c>
@@ -8454,12 +8450,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
         <v>314</v>
       </c>
@@ -8522,7 +8518,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="85" customWidth="1"/>
@@ -8630,7 +8626,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="32">
+    <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
         <v>341</v>
       </c>
@@ -8689,7 +8685,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:N27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="24" customWidth="1"/>
@@ -9716,7 +9712,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="128">
+    <row r="27" spans="1:14" ht="124">
       <c r="A27" s="26" t="s">
         <v>826</v>
       </c>

--- a/RWF_Films.xlsx
+++ b/RWF_Films.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/23f243e0dd638448/cours/KH/RWF/Fiches/Frise/Frise2_Fassbinder/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="63" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B33C91-36F2-DE40-9621-665068ED7DF4}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="11_C02D27A5C2B52CDF254B06CC0F60AB0FB8A300C2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7993DFE3-928A-B240-8865-56D5E195CC90}"/>
   <bookViews>
-    <workbookView xWindow="19100" yWindow="600" windowWidth="22240" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8060" yWindow="600" windowWidth="33280" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Films" sheetId="1" r:id="rId1"/>
@@ -1046,9 +1046,6 @@
     <t>film-1978-l-annee-des-treize-lunes</t>
   </si>
   <si>
-    <t>rwf-1978-maria-braun</t>
-  </si>
-  <si>
     <t>Le Mariage de Maria Braun</t>
   </si>
   <si>
@@ -1056,9 +1053,6 @@
   </si>
   <si>
     <t>Films_images/Le_Mariage_de_Maria_Braun.jpg</t>
-  </si>
-  <si>
-    <t>film-1978-le-mariage-de-maria-braun</t>
   </si>
   <si>
     <t>rwf-1979-la-troisieme-generation</t>
@@ -3438,6 +3432,12 @@
 Lilo Pempeit : Mme Ehmke
 Karl-Heinz von Hassel : le procureur général
 Rainer Werner Fassbinder : l’homme du marché noir</t>
+  </si>
+  <si>
+    <t>rwf-1979-maria-braun</t>
+  </si>
+  <si>
+    <t>film-1979-le-mariage-de-maria-braun</t>
   </si>
 </sst>
 </file>
@@ -4944,13 +4944,13 @@
     </row>
     <row r="2" spans="1:30" s="37" customFormat="1" ht="107" customHeight="1">
       <c r="A2" s="34" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="B2" s="35" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C2" s="35" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="D2" s="35">
         <v>1966</v>
@@ -4996,7 +4996,7 @@
         <v>31</v>
       </c>
       <c r="C3" s="27" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D3" s="27">
         <v>1966</v>
@@ -5017,22 +5017,22 @@
         <v>34</v>
       </c>
       <c r="J3" s="27" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="K3" s="27"/>
       <c r="L3" s="27"/>
       <c r="M3" s="27"/>
       <c r="N3" s="27" t="s">
+        <v>582</v>
+      </c>
+      <c r="O3" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="P3" s="27" t="s">
         <v>584</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="Q3" s="27" t="s">
         <v>585</v>
-      </c>
-      <c r="P3" s="27" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q3" s="27" t="s">
-        <v>587</v>
       </c>
       <c r="R3" s="27"/>
       <c r="S3" s="27"/>
@@ -5043,7 +5043,7 @@
       <c r="X3" s="27"/>
       <c r="Y3" s="27"/>
       <c r="Z3" s="27" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AA3" s="27"/>
       <c r="AB3" s="1" t="s">
@@ -5060,7 +5060,7 @@
         <v>37</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D4" s="27">
         <v>1967</v>
@@ -5081,22 +5081,22 @@
         <v>34</v>
       </c>
       <c r="J4" s="27" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="K4" s="27"/>
       <c r="L4" s="27"/>
       <c r="M4" s="27"/>
       <c r="N4" s="27" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="O4" s="27" t="s">
+        <v>589</v>
+      </c>
+      <c r="P4" s="27" t="s">
+        <v>590</v>
+      </c>
+      <c r="Q4" s="27" t="s">
         <v>591</v>
-      </c>
-      <c r="P4" s="27" t="s">
-        <v>592</v>
-      </c>
-      <c r="Q4" s="27" t="s">
-        <v>593</v>
       </c>
       <c r="R4" s="27"/>
       <c r="S4" s="27"/>
@@ -5107,7 +5107,7 @@
       <c r="X4" s="27"/>
       <c r="Y4" s="27"/>
       <c r="Z4" s="27" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="AA4" s="27"/>
       <c r="AB4" s="9" t="s">
@@ -5146,25 +5146,25 @@
       </c>
       <c r="J5" s="28"/>
       <c r="K5" s="28" t="s">
+        <v>593</v>
+      </c>
+      <c r="L5" s="28" t="s">
+        <v>594</v>
+      </c>
+      <c r="M5" s="28" t="s">
         <v>595</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="N5" s="28" t="s">
         <v>596</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="O5" s="28" t="s">
         <v>597</v>
       </c>
-      <c r="N5" s="28" t="s">
+      <c r="P5" s="28" t="s">
         <v>598</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="Q5" s="28" t="s">
         <v>599</v>
-      </c>
-      <c r="P5" s="28" t="s">
-        <v>600</v>
-      </c>
-      <c r="Q5" s="28" t="s">
-        <v>601</v>
       </c>
       <c r="R5" s="28"/>
       <c r="S5" s="28"/>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="Y5" s="28"/>
       <c r="Z5" s="28" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AA5" s="28" t="s">
         <v>45</v>
@@ -5235,20 +5235,20 @@
         <v>173</v>
       </c>
       <c r="N6" s="28" t="s">
+        <v>601</v>
+      </c>
+      <c r="O6" s="28" t="s">
+        <v>602</v>
+      </c>
+      <c r="P6" s="28" t="s">
         <v>603</v>
       </c>
-      <c r="O6" s="28" t="s">
+      <c r="Q6" s="28" t="s">
         <v>604</v>
-      </c>
-      <c r="P6" s="28" t="s">
-        <v>605</v>
-      </c>
-      <c r="Q6" s="28" t="s">
-        <v>606</v>
       </c>
       <c r="R6" s="28"/>
       <c r="S6" s="28" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="T6" s="28"/>
       <c r="U6" s="28" t="s">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="Y6" s="28"/>
       <c r="Z6" s="28" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="AA6" s="28" t="s">
         <v>45</v>
@@ -5286,7 +5286,7 @@
         <v>53</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D7" s="38">
         <v>1970</v>
@@ -5319,16 +5319,16 @@
         <v>173</v>
       </c>
       <c r="N7" s="28" t="s">
+        <v>607</v>
+      </c>
+      <c r="O7" s="28" t="s">
+        <v>608</v>
+      </c>
+      <c r="P7" s="28" t="s">
         <v>609</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="Q7" s="28" t="s">
         <v>610</v>
-      </c>
-      <c r="P7" s="28" t="s">
-        <v>611</v>
-      </c>
-      <c r="Q7" s="28" t="s">
-        <v>612</v>
       </c>
       <c r="R7" s="28"/>
       <c r="S7" s="28"/>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="Y7" s="28"/>
       <c r="Z7" s="28" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="AA7" s="28" t="s">
         <v>45</v>
@@ -5368,7 +5368,7 @@
         <v>58</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D8" s="38">
         <v>1970</v>
@@ -5386,13 +5386,13 @@
         <v>59</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="J8" s="28" t="s">
         <v>102</v>
       </c>
       <c r="K8" s="28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="L8" s="28" t="s">
         <v>104</v>
@@ -5401,16 +5401,16 @@
         <v>173</v>
       </c>
       <c r="N8" s="28" t="s">
+        <v>613</v>
+      </c>
+      <c r="O8" s="28" t="s">
+        <v>614</v>
+      </c>
+      <c r="P8" s="28" t="s">
         <v>615</v>
       </c>
-      <c r="O8" s="28" t="s">
+      <c r="Q8" s="28" t="s">
         <v>616</v>
-      </c>
-      <c r="P8" s="28" t="s">
-        <v>617</v>
-      </c>
-      <c r="Q8" s="28" t="s">
-        <v>618</v>
       </c>
       <c r="R8" s="28"/>
       <c r="S8" s="28"/>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="Y8" s="28"/>
       <c r="Z8" s="28" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="AA8" s="28" t="s">
         <v>45</v>
@@ -5448,7 +5448,7 @@
         <v>62</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D9" s="38">
         <v>1970</v>
@@ -5475,22 +5475,22 @@
         <v>145</v>
       </c>
       <c r="L9" s="28" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="M9" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N9" s="28" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="O9" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q9" s="28" t="s">
         <v>622</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>623</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>624</v>
       </c>
       <c r="R9" s="28"/>
       <c r="S9" s="28"/>
@@ -5505,7 +5505,7 @@
       </c>
       <c r="Y9" s="28"/>
       <c r="Z9" s="28" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="AA9" s="28" t="s">
         <v>45</v>
@@ -5530,7 +5530,7 @@
         <v>66</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D10" s="38">
         <v>1970</v>
@@ -5548,13 +5548,13 @@
         <v>34</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="J10" s="28" t="s">
         <v>102</v>
       </c>
       <c r="K10" s="28" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L10" s="28" t="s">
         <v>104</v>
@@ -5563,13 +5563,13 @@
         <v>173</v>
       </c>
       <c r="N10" s="28" t="s">
+        <v>626</v>
+      </c>
+      <c r="O10" s="28" t="s">
+        <v>627</v>
+      </c>
+      <c r="P10" s="28" t="s">
         <v>628</v>
-      </c>
-      <c r="O10" s="28" t="s">
-        <v>629</v>
-      </c>
-      <c r="P10" s="28" t="s">
-        <v>630</v>
       </c>
       <c r="Q10" s="28"/>
       <c r="R10" s="28"/>
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Y10" s="28"/>
       <c r="Z10" s="28" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="AA10" s="28" t="s">
         <v>45</v>
@@ -5602,13 +5602,13 @@
     </row>
     <row r="11" spans="1:30" ht="227.75" customHeight="1">
       <c r="A11" s="28" t="s">
+        <v>844</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>845</v>
+      </c>
+      <c r="C11" s="28" t="s">
         <v>846</v>
-      </c>
-      <c r="B11" s="28" t="s">
-        <v>847</v>
-      </c>
-      <c r="C11" s="28" t="s">
-        <v>848</v>
       </c>
       <c r="D11" s="38">
         <v>1970</v>
@@ -5676,7 +5676,7 @@
         <v>102</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L12" s="28" t="s">
         <v>104</v>
@@ -5685,16 +5685,16 @@
         <v>173</v>
       </c>
       <c r="N12" s="28" t="s">
+        <v>630</v>
+      </c>
+      <c r="O12" s="28" t="s">
+        <v>631</v>
+      </c>
+      <c r="P12" s="28" t="s">
         <v>632</v>
       </c>
-      <c r="O12" s="28" t="s">
+      <c r="Q12" s="28" t="s">
         <v>633</v>
-      </c>
-      <c r="P12" s="28" t="s">
-        <v>634</v>
-      </c>
-      <c r="Q12" s="28" t="s">
-        <v>635</v>
       </c>
       <c r="R12" s="28"/>
       <c r="S12" s="28"/>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="Y12" s="28"/>
       <c r="Z12" s="28" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="AA12" s="28"/>
       <c r="AB12" s="1" t="s">
@@ -5746,7 +5746,7 @@
         <v>159</v>
       </c>
       <c r="K13" s="28" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="L13" s="28" t="s">
         <v>104</v>
@@ -5755,16 +5755,16 @@
         <v>173</v>
       </c>
       <c r="N13" s="28" t="s">
+        <v>635</v>
+      </c>
+      <c r="O13" s="28" t="s">
+        <v>636</v>
+      </c>
+      <c r="P13" s="28" t="s">
         <v>637</v>
       </c>
-      <c r="O13" s="28" t="s">
+      <c r="Q13" s="28" t="s">
         <v>638</v>
-      </c>
-      <c r="P13" s="28" t="s">
-        <v>639</v>
-      </c>
-      <c r="Q13" s="28" t="s">
-        <v>640</v>
       </c>
       <c r="R13" s="28"/>
       <c r="S13" s="28"/>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Y13" s="28"/>
       <c r="Z13" s="28" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="AA13" s="28" t="s">
         <v>45</v>
@@ -5802,7 +5802,7 @@
         <v>78</v>
       </c>
       <c r="C14" s="28" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="D14" s="38">
         <v>1971</v>
@@ -5826,7 +5826,7 @@
         <v>159</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="L14" s="28" t="s">
         <v>104</v>
@@ -5835,20 +5835,20 @@
         <v>173</v>
       </c>
       <c r="N14" s="28" t="s">
+        <v>642</v>
+      </c>
+      <c r="O14" s="28" t="s">
+        <v>643</v>
+      </c>
+      <c r="P14" s="28" t="s">
         <v>644</v>
       </c>
-      <c r="O14" s="28" t="s">
+      <c r="Q14" s="28" t="s">
         <v>645</v>
-      </c>
-      <c r="P14" s="28" t="s">
-        <v>646</v>
-      </c>
-      <c r="Q14" s="28" t="s">
-        <v>647</v>
       </c>
       <c r="R14" s="28"/>
       <c r="S14" s="28" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="T14" s="28"/>
       <c r="U14" s="28" t="s">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="Y14" s="28"/>
       <c r="Z14" s="28" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AA14" s="28" t="s">
         <v>45</v>
@@ -5886,7 +5886,7 @@
         <v>82</v>
       </c>
       <c r="C15" s="28" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D15" s="38">
         <v>1971</v>
@@ -5904,7 +5904,7 @@
         <v>34</v>
       </c>
       <c r="I15" s="28" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="J15" s="28" t="s">
         <v>102</v>
@@ -5919,16 +5919,16 @@
         <v>173</v>
       </c>
       <c r="N15" s="28" t="s">
+        <v>649</v>
+      </c>
+      <c r="O15" s="28" t="s">
+        <v>650</v>
+      </c>
+      <c r="P15" s="28" t="s">
         <v>651</v>
       </c>
-      <c r="O15" s="28" t="s">
+      <c r="Q15" s="28" t="s">
         <v>652</v>
-      </c>
-      <c r="P15" s="28" t="s">
-        <v>653</v>
-      </c>
-      <c r="Q15" s="28" t="s">
-        <v>654</v>
       </c>
       <c r="R15" s="28"/>
       <c r="S15" s="28"/>
@@ -5941,7 +5941,7 @@
       </c>
       <c r="Y15" s="28"/>
       <c r="Z15" s="28" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="AA15" s="28" t="s">
         <v>45</v>
@@ -5997,16 +5997,16 @@
       </c>
       <c r="M16" s="28"/>
       <c r="N16" s="28" t="s">
+        <v>654</v>
+      </c>
+      <c r="O16" s="28" t="s">
+        <v>655</v>
+      </c>
+      <c r="P16" s="28" t="s">
         <v>656</v>
       </c>
-      <c r="O16" s="28" t="s">
+      <c r="Q16" s="28" t="s">
         <v>657</v>
-      </c>
-      <c r="P16" s="28" t="s">
-        <v>658</v>
-      </c>
-      <c r="Q16" s="28" t="s">
-        <v>659</v>
       </c>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="Y16" s="28"/>
       <c r="Z16" s="28" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="AA16" s="28" t="s">
         <v>45</v>
@@ -6064,7 +6064,7 @@
         <v>34</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="J17" s="28" t="s">
         <v>159</v>
@@ -6080,13 +6080,13 @@
         <v>187</v>
       </c>
       <c r="O17" s="28" t="s">
+        <v>660</v>
+      </c>
+      <c r="P17" s="28" t="s">
+        <v>661</v>
+      </c>
+      <c r="Q17" s="28" t="s">
         <v>662</v>
-      </c>
-      <c r="P17" s="28" t="s">
-        <v>663</v>
-      </c>
-      <c r="Q17" s="28" t="s">
-        <v>664</v>
       </c>
       <c r="R17" s="28"/>
       <c r="S17" s="28"/>
@@ -6101,7 +6101,7 @@
       </c>
       <c r="Y17" s="28"/>
       <c r="Z17" s="28" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="AA17" s="28" t="s">
         <v>45</v>
@@ -6126,7 +6126,7 @@
         <v>96</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D18" s="38">
         <v>1972</v>
@@ -6144,29 +6144,29 @@
         <v>34</v>
       </c>
       <c r="I18" s="28" t="s">
+        <v>665</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>666</v>
+      </c>
+      <c r="K18" s="28" t="s">
         <v>667</v>
-      </c>
-      <c r="J18" s="28" t="s">
-        <v>668</v>
-      </c>
-      <c r="K18" s="28" t="s">
-        <v>669</v>
       </c>
       <c r="L18" s="28" t="s">
         <v>104</v>
       </c>
       <c r="M18" s="28"/>
       <c r="N18" s="28" t="s">
+        <v>668</v>
+      </c>
+      <c r="O18" s="28" t="s">
+        <v>669</v>
+      </c>
+      <c r="P18" s="28" t="s">
         <v>670</v>
       </c>
-      <c r="O18" s="28" t="s">
+      <c r="Q18" s="28" t="s">
         <v>671</v>
-      </c>
-      <c r="P18" s="28" t="s">
-        <v>672</v>
-      </c>
-      <c r="Q18" s="28" t="s">
-        <v>673</v>
       </c>
       <c r="R18" s="28"/>
       <c r="S18" s="28"/>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="Y18" s="28"/>
       <c r="Z18" s="28" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="AA18" s="28" t="s">
         <v>45</v>
@@ -6284,7 +6284,7 @@
         <v>115</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D20" s="38">
         <v>1973</v>
@@ -6302,7 +6302,7 @@
         <v>34</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J20" s="28" t="s">
         <v>102</v>
@@ -6314,19 +6314,19 @@
         <v>104</v>
       </c>
       <c r="M20" s="28" t="s">
+        <v>675</v>
+      </c>
+      <c r="N20" s="28" t="s">
+        <v>676</v>
+      </c>
+      <c r="O20" s="28" t="s">
         <v>677</v>
       </c>
-      <c r="N20" s="28" t="s">
+      <c r="P20" s="28" t="s">
         <v>678</v>
       </c>
-      <c r="O20" s="28" t="s">
+      <c r="Q20" s="28" t="s">
         <v>679</v>
-      </c>
-      <c r="P20" s="28" t="s">
-        <v>680</v>
-      </c>
-      <c r="Q20" s="28" t="s">
-        <v>681</v>
       </c>
       <c r="R20" s="28"/>
       <c r="S20" s="28"/>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="Y20" s="28"/>
       <c r="Z20" s="28" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="AA20" s="28" t="s">
         <v>45</v>
@@ -6614,29 +6614,29 @@
         <v>34</v>
       </c>
       <c r="I24" s="28" t="s">
+        <v>681</v>
+      </c>
+      <c r="J24" s="28" t="s">
+        <v>682</v>
+      </c>
+      <c r="K24" s="28" t="s">
         <v>683</v>
       </c>
-      <c r="J24" s="28" t="s">
+      <c r="L24" s="28" t="s">
         <v>684</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>685</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>686</v>
       </c>
       <c r="M24" s="28"/>
       <c r="N24" s="28" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="O24" s="28" t="s">
+        <v>685</v>
+      </c>
+      <c r="P24" s="28" t="s">
+        <v>686</v>
+      </c>
+      <c r="Q24" s="28" t="s">
         <v>687</v>
-      </c>
-      <c r="P24" s="28" t="s">
-        <v>688</v>
-      </c>
-      <c r="Q24" s="28" t="s">
-        <v>689</v>
       </c>
       <c r="R24" s="28"/>
       <c r="S24" s="28"/>
@@ -6649,7 +6649,7 @@
       </c>
       <c r="Y24" s="28"/>
       <c r="Z24" s="28" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="AA24" s="28" t="s">
         <v>45</v>
@@ -6930,7 +6930,7 @@
         <v>197</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D28" s="38">
         <v>1975</v>
@@ -6948,29 +6948,29 @@
         <v>34</v>
       </c>
       <c r="I28" s="28" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="J28" s="28" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="K28" s="28"/>
       <c r="L28" s="28" t="s">
         <v>104</v>
       </c>
       <c r="M28" s="28" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="N28" s="28" t="s">
         <v>105</v>
       </c>
       <c r="O28" s="28" t="s">
+        <v>693</v>
+      </c>
+      <c r="P28" s="28" t="s">
+        <v>694</v>
+      </c>
+      <c r="Q28" s="28" t="s">
         <v>695</v>
-      </c>
-      <c r="P28" s="28" t="s">
-        <v>696</v>
-      </c>
-      <c r="Q28" s="28" t="s">
-        <v>697</v>
       </c>
       <c r="R28" s="28"/>
       <c r="S28" s="28"/>
@@ -6983,7 +6983,7 @@
       </c>
       <c r="Y28" s="28"/>
       <c r="Z28" s="28" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="AA28" s="28" t="s">
         <v>45</v>
@@ -7008,7 +7008,7 @@
         <v>200</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D29" s="38">
         <v>1975</v>
@@ -7026,13 +7026,13 @@
         <v>34</v>
       </c>
       <c r="I29" s="28" t="s">
+        <v>698</v>
+      </c>
+      <c r="J29" s="28" t="s">
+        <v>699</v>
+      </c>
+      <c r="K29" s="28" t="s">
         <v>700</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>701</v>
-      </c>
-      <c r="K29" s="28" t="s">
-        <v>702</v>
       </c>
       <c r="L29" s="28" t="s">
         <v>104</v>
@@ -7041,16 +7041,16 @@
         <v>173</v>
       </c>
       <c r="N29" s="28" t="s">
+        <v>701</v>
+      </c>
+      <c r="O29" s="28" t="s">
+        <v>702</v>
+      </c>
+      <c r="P29" s="28" t="s">
         <v>703</v>
       </c>
-      <c r="O29" s="28" t="s">
+      <c r="Q29" s="28" t="s">
         <v>704</v>
-      </c>
-      <c r="P29" s="28" t="s">
-        <v>705</v>
-      </c>
-      <c r="Q29" s="28" t="s">
-        <v>706</v>
       </c>
       <c r="R29" s="28"/>
       <c r="S29" s="28"/>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="Y29" s="28"/>
       <c r="Z29" s="28" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="AA29" s="28" t="s">
         <v>45</v>
@@ -7088,7 +7088,7 @@
         <v>203</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D30" s="38">
         <v>1976</v>
@@ -7103,32 +7103,32 @@
         <v>33</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="J30" s="28" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="K30" s="28" t="s">
         <v>224</v>
       </c>
       <c r="L30" s="28"/>
       <c r="M30" s="28" t="s">
+        <v>709</v>
+      </c>
+      <c r="N30" s="28" t="s">
+        <v>710</v>
+      </c>
+      <c r="O30" s="28" t="s">
         <v>711</v>
       </c>
-      <c r="N30" s="28" t="s">
+      <c r="P30" s="28" t="s">
         <v>712</v>
       </c>
-      <c r="O30" s="28" t="s">
+      <c r="Q30" s="28" t="s">
         <v>713</v>
-      </c>
-      <c r="P30" s="28" t="s">
-        <v>714</v>
-      </c>
-      <c r="Q30" s="28" t="s">
-        <v>715</v>
       </c>
       <c r="R30" s="28"/>
       <c r="S30" s="28"/>
@@ -7143,7 +7143,7 @@
       </c>
       <c r="Y30" s="28"/>
       <c r="Z30" s="28" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="AA30" s="28" t="s">
         <v>45</v>
@@ -7422,7 +7422,7 @@
         <v>245</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D34" s="38">
         <v>1977</v>
@@ -7440,27 +7440,27 @@
         <v>34</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="J34" s="28" t="s">
         <v>159</v>
       </c>
       <c r="K34" s="28" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="L34" s="28" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="M34" s="28"/>
       <c r="N34" s="28"/>
       <c r="O34" s="28" t="s">
+        <v>719</v>
+      </c>
+      <c r="P34" s="28" t="s">
+        <v>720</v>
+      </c>
+      <c r="Q34" s="28" t="s">
         <v>721</v>
-      </c>
-      <c r="P34" s="28" t="s">
-        <v>722</v>
-      </c>
-      <c r="Q34" s="28" t="s">
-        <v>723</v>
       </c>
       <c r="R34" s="28"/>
       <c r="S34" s="30"/>
@@ -7473,7 +7473,7 @@
       </c>
       <c r="Y34" s="28"/>
       <c r="Z34" s="28" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="AA34" s="28" t="s">
         <v>45</v>
@@ -7498,7 +7498,7 @@
         <v>249</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D35" s="38">
         <v>1977</v>
@@ -7516,7 +7516,7 @@
         <v>34</v>
       </c>
       <c r="I35" s="28" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="J35" s="28" t="s">
         <v>159</v>
@@ -7527,16 +7527,16 @@
         <v>173</v>
       </c>
       <c r="N35" s="28" t="s">
+        <v>725</v>
+      </c>
+      <c r="O35" s="28" t="s">
+        <v>726</v>
+      </c>
+      <c r="P35" s="28" t="s">
         <v>727</v>
       </c>
-      <c r="O35" s="28" t="s">
+      <c r="Q35" s="28" t="s">
         <v>728</v>
-      </c>
-      <c r="P35" s="28" t="s">
-        <v>729</v>
-      </c>
-      <c r="Q35" s="28" t="s">
-        <v>730</v>
       </c>
       <c r="R35" s="28"/>
       <c r="S35" s="28"/>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="Y35" s="28"/>
       <c r="Z35" s="28" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="AA35" s="28" t="s">
         <v>45</v>
@@ -7720,7 +7720,7 @@
         <v>273</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D38" s="38">
         <v>1978</v>
@@ -7744,30 +7744,30 @@
         <v>34</v>
       </c>
       <c r="K38" s="28" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="L38" s="28"/>
       <c r="M38" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N38" s="28" t="s">
+        <v>732</v>
+      </c>
+      <c r="O38" s="28" t="s">
+        <v>733</v>
+      </c>
+      <c r="P38" s="28" t="s">
         <v>734</v>
       </c>
-      <c r="O38" s="28" t="s">
+      <c r="Q38" s="28" t="s">
         <v>735</v>
-      </c>
-      <c r="P38" s="28" t="s">
-        <v>736</v>
-      </c>
-      <c r="Q38" s="28" t="s">
-        <v>737</v>
       </c>
       <c r="R38" s="28"/>
       <c r="S38" s="31" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="T38" s="28" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="U38" s="28" t="s">
         <v>274</v>
@@ -7778,7 +7778,7 @@
         <v>258</v>
       </c>
       <c r="Y38" s="28" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="Z38" s="28" t="s">
         <v>111</v>
@@ -7800,16 +7800,16 @@
     </row>
     <row r="39" spans="1:30" ht="409.6">
       <c r="A39" s="28" t="s">
+        <v>850</v>
+      </c>
+      <c r="B39" s="28" t="s">
         <v>276</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="C39" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="C39" s="28" t="s">
-        <v>278</v>
-      </c>
       <c r="D39" s="38">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="E39" s="28" t="s">
         <v>42</v>
@@ -7824,7 +7824,7 @@
         <v>34</v>
       </c>
       <c r="I39" s="28" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="J39" s="28" t="s">
         <v>159</v>
@@ -7835,34 +7835,34 @@
         <v>173</v>
       </c>
       <c r="N39" s="28" t="s">
+        <v>738</v>
+      </c>
+      <c r="O39" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="P39" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="Q39" s="28" t="s">
         <v>740</v>
-      </c>
-      <c r="O39" s="28" t="s">
-        <v>851</v>
-      </c>
-      <c r="P39" s="28" t="s">
-        <v>741</v>
-      </c>
-      <c r="Q39" s="28" t="s">
-        <v>742</v>
       </c>
       <c r="R39" s="28"/>
       <c r="S39" s="28" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="T39" s="28" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="U39" s="28" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="V39" s="28"/>
       <c r="W39" s="28"/>
       <c r="X39" s="32" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Y39" s="28" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="Z39" s="28" t="s">
         <v>111</v>
@@ -7871,7 +7871,7 @@
         <v>112</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>280</v>
+        <v>851</v>
       </c>
       <c r="AC39" s="6" t="str">
         <f>IF(O39="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O39)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O39)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O39)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O39)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O39)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O39)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O39)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O39)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O39)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O39)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O39)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O39)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O39)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O39)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O39)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O39)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O39)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O39)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O39)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O39)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O39)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O39)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O39)),'Référentiel entourage'!$A$24,"")))</f>
@@ -7884,13 +7884,13 @@
     </row>
     <row r="40" spans="1:30" ht="228">
       <c r="A40" s="28" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B40" s="28" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C40" s="28" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D40" s="38">
         <v>1979</v>
@@ -7914,44 +7914,44 @@
         <v>34</v>
       </c>
       <c r="K40" s="28" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L40" s="28"/>
       <c r="M40" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N40" s="28" t="s">
+        <v>745</v>
+      </c>
+      <c r="O40" s="28" t="s">
+        <v>746</v>
+      </c>
+      <c r="P40" s="28" t="s">
         <v>747</v>
       </c>
-      <c r="O40" s="28" t="s">
+      <c r="Q40" s="28" t="s">
         <v>748</v>
-      </c>
-      <c r="P40" s="28" t="s">
-        <v>749</v>
-      </c>
-      <c r="Q40" s="28" t="s">
-        <v>750</v>
       </c>
       <c r="R40" s="28"/>
       <c r="S40" s="28"/>
       <c r="T40" s="28"/>
       <c r="U40" s="28" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="V40" s="28"/>
       <c r="W40" s="28"/>
       <c r="X40" s="28" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="Y40" s="28"/>
       <c r="Z40" s="28" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AA40" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AC40" s="6" t="str">
         <f>IF(O40="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O40)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O40)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O40)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O40)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O40)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O40)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O40)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O40)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O40)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O40)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O40)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O40)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O40)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O40)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O40)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O40)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O40)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O40)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O40)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O40)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O40)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O40)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O40)),'Référentiel entourage'!$A$24,"")))</f>
@@ -7964,13 +7964,13 @@
     </row>
     <row r="41" spans="1:30" ht="409.6">
       <c r="A41" s="28" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B41" s="28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C41" s="28" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D41" s="38">
         <v>1980</v>
@@ -7988,52 +7988,52 @@
         <v>34</v>
       </c>
       <c r="I41" s="28" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J41" s="28" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K41" s="28" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="L41" s="28"/>
       <c r="M41" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N41" s="28" t="s">
+        <v>752</v>
+      </c>
+      <c r="O41" s="28" t="s">
+        <v>753</v>
+      </c>
+      <c r="P41" s="28" t="s">
         <v>754</v>
       </c>
-      <c r="O41" s="28" t="s">
+      <c r="Q41" s="28" t="s">
         <v>755</v>
-      </c>
-      <c r="P41" s="28" t="s">
-        <v>756</v>
-      </c>
-      <c r="Q41" s="28" t="s">
-        <v>757</v>
       </c>
       <c r="R41" s="28"/>
       <c r="S41" s="28" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="T41" s="28"/>
       <c r="U41" s="28" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="V41" s="28"/>
       <c r="W41" s="28"/>
       <c r="X41" s="28" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="Y41" s="28"/>
       <c r="Z41" s="28" t="s">
         <v>111</v>
       </c>
       <c r="AA41" s="28" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AC41" s="6" t="str">
         <f>IF(O41="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O41)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O41)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O41)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O41)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O41)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O41)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O41)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O41)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O41)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O41)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O41)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O41)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O41)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O41)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O41)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O41)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O41)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O41)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O41)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O41)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O41)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O41)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O41)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8046,13 +8046,13 @@
     </row>
     <row r="42" spans="1:30" ht="409.6">
       <c r="A42" s="28" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C42" s="28" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D42" s="38">
         <v>1981</v>
@@ -8070,52 +8070,52 @@
         <v>34</v>
       </c>
       <c r="I42" s="28" t="s">
+        <v>756</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>757</v>
+      </c>
+      <c r="K42" s="28" t="s">
         <v>758</v>
-      </c>
-      <c r="J42" s="28" t="s">
-        <v>759</v>
-      </c>
-      <c r="K42" s="28" t="s">
-        <v>760</v>
       </c>
       <c r="L42" s="28"/>
       <c r="M42" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N42" s="28" t="s">
+        <v>759</v>
+      </c>
+      <c r="O42" s="28" t="s">
+        <v>760</v>
+      </c>
+      <c r="P42" s="28" t="s">
         <v>761</v>
       </c>
-      <c r="O42" s="28" t="s">
-        <v>762</v>
-      </c>
-      <c r="P42" s="28" t="s">
-        <v>763</v>
-      </c>
       <c r="Q42" s="28" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="R42" s="28"/>
       <c r="S42" s="28" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="T42" s="28"/>
       <c r="U42" s="28" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="V42" s="28"/>
       <c r="W42" s="28"/>
       <c r="X42" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Y42" s="28"/>
       <c r="Z42" s="28" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="AA42" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="AC42" s="6" t="str">
         <f>IF(O42="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O42)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O42)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O42)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O42)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O42)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O42)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O42)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O42)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O42)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O42)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O42)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O42)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O42)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O42)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O42)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O42)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O42)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O42)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O42)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O42)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O42)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O42)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O42)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8128,19 +8128,19 @@
     </row>
     <row r="43" spans="1:30" ht="76">
       <c r="A43" s="28" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B43" s="28" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C43" s="28" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D43" s="38">
         <v>1981</v>
       </c>
       <c r="E43" s="28" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="F43" s="29">
         <v>91</v>
@@ -8159,14 +8159,14 @@
       <c r="L43" s="28"/>
       <c r="M43" s="28"/>
       <c r="N43" s="28" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="O43" s="28"/>
       <c r="P43" s="28" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Q43" s="28" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="R43" s="28"/>
       <c r="S43" s="28"/>
@@ -8175,17 +8175,17 @@
       <c r="V43" s="28"/>
       <c r="W43" s="28"/>
       <c r="X43" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Y43" s="28"/>
       <c r="Z43" s="28" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="AA43" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="AC43" s="6" t="str">
         <f>IF(O43="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O43)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O43)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O43)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O43)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O43)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O43)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O43)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O43)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O43)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O43)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O43)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O43)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O43)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O43)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O43)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O43)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O43)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O43)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O43)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O43)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O43)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O43)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O43)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8198,13 +8198,13 @@
     </row>
     <row r="44" spans="1:30" ht="304">
       <c r="A44" s="28" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B44" s="28" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C44" s="28" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D44" s="38">
         <v>1981</v>
@@ -8222,50 +8222,50 @@
         <v>34</v>
       </c>
       <c r="I44" s="28" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="J44" s="28" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K44" s="28" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L44" s="28"/>
       <c r="M44" s="28" t="s">
+        <v>770</v>
+      </c>
+      <c r="N44" s="28" t="s">
+        <v>771</v>
+      </c>
+      <c r="O44" s="28" t="s">
         <v>772</v>
       </c>
-      <c r="N44" s="28" t="s">
+      <c r="P44" s="28" t="s">
         <v>773</v>
       </c>
-      <c r="O44" s="28" t="s">
+      <c r="Q44" s="28" t="s">
         <v>774</v>
-      </c>
-      <c r="P44" s="28" t="s">
-        <v>775</v>
-      </c>
-      <c r="Q44" s="28" t="s">
-        <v>776</v>
       </c>
       <c r="R44" s="28"/>
       <c r="S44" s="28"/>
       <c r="T44" s="28"/>
       <c r="U44" s="28" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="V44" s="28"/>
       <c r="W44" s="28"/>
       <c r="X44" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Y44" s="28"/>
       <c r="Z44" s="28" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="AA44" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="AC44" s="6" t="str">
         <f>IF(O44="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O44)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O44)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O44)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O44)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O44)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O44)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O44)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O44)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O44)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O44)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O44)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O44)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O44)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O44)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O44)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O44)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O44)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O44)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O44)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O44)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O44)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O44)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O44)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8278,13 +8278,13 @@
     </row>
     <row r="45" spans="1:30" ht="380">
       <c r="A45" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>303</v>
+      </c>
+      <c r="C45" s="28" t="s">
         <v>304</v>
-      </c>
-      <c r="B45" s="28" t="s">
-        <v>305</v>
-      </c>
-      <c r="C45" s="28" t="s">
-        <v>306</v>
       </c>
       <c r="D45" s="38">
         <v>1981</v>
@@ -8306,32 +8306,32 @@
       <c r="M45" s="28"/>
       <c r="N45" s="28"/>
       <c r="O45" s="28" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="P45" s="28"/>
       <c r="Q45" s="28" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="R45" s="28"/>
       <c r="S45" s="28"/>
       <c r="T45" s="28"/>
       <c r="U45" s="28" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="V45" s="28"/>
       <c r="W45" s="28"/>
       <c r="X45" s="28" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Y45" s="28"/>
       <c r="Z45" s="28" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="AA45" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AC45" s="6" t="str">
         <f>IF(O45="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O45)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O45)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O45)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O45)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O45)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O45)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O45)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O45)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O45)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O45)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O45)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O45)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O45)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O45)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O45)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O45)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O45)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O45)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O45)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O45)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O45)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O45)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O45)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8344,13 +8344,13 @@
     </row>
     <row r="46" spans="1:30" ht="342">
       <c r="A46" s="28" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B46" s="28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C46" s="28" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D46" s="38">
         <v>1982</v>
@@ -8368,52 +8368,52 @@
         <v>34</v>
       </c>
       <c r="I46" s="28" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="J46" s="28" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="K46" s="28" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="L46" s="28" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="M46" s="28" t="s">
         <v>173</v>
       </c>
       <c r="N46" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="O46" s="28" t="s">
+        <v>782</v>
+      </c>
+      <c r="P46" s="28" t="s">
         <v>783</v>
       </c>
-      <c r="O46" s="28" t="s">
+      <c r="Q46" s="28" t="s">
         <v>784</v>
-      </c>
-      <c r="P46" s="28" t="s">
-        <v>785</v>
-      </c>
-      <c r="Q46" s="28" t="s">
-        <v>786</v>
       </c>
       <c r="R46" s="28"/>
       <c r="S46" s="28"/>
       <c r="T46" s="28"/>
       <c r="U46" s="28" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="V46" s="28"/>
       <c r="W46" s="28"/>
       <c r="X46" s="28" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="Y46" s="28"/>
       <c r="Z46" s="28" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="AA46" s="28" t="s">
         <v>45</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="AC46" s="6" t="str">
         <f>IF(O46="","",_xlfn.TEXTJOIN("; ",TRUE,IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$2,O46)),'Référentiel entourage'!$A$2,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$3,O46)),'Référentiel entourage'!$A$3,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$4,O46)),'Référentiel entourage'!$A$4,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$5,O46)),'Référentiel entourage'!$A$5,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$6,O46)),'Référentiel entourage'!$A$6,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$7,O46)),'Référentiel entourage'!$A$7,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$8,O46)),'Référentiel entourage'!$A$8,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$9,O46)),'Référentiel entourage'!$A$9,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$10,O46)),'Référentiel entourage'!$A$10,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$11,O46)),'Référentiel entourage'!$A$11,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$12,O46)),'Référentiel entourage'!$A$12,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$13,O46)),'Référentiel entourage'!$A$13,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$14,O46)),'Référentiel entourage'!$A$14,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$15,O46)),'Référentiel entourage'!$A$15,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$16,O46)),'Référentiel entourage'!$A$16,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$17,O46)),'Référentiel entourage'!$A$17,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$18,O46)),'Référentiel entourage'!$A$18,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$19,O46)),'Référentiel entourage'!$A$19,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$20,O46)),'Référentiel entourage'!$A$20,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$21,O46)),'Référentiel entourage'!$A$21,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$22,O46)),'Référentiel entourage'!$A$22,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$23,O46)),'Référentiel entourage'!$A$23,""),IF(ISNUMBER(SEARCH('Référentiel entourage'!$B$24,O46)),'Référentiel entourage'!$A$24,"")))</f>
@@ -8457,10 +8457,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="15">
       <c r="A1" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8473,10 +8473,10 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8484,7 +8484,7 @@
         <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8492,22 +8492,22 @@
         <v>101</v>
       </c>
       <c r="B5" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -8526,32 +8526,32 @@
   <sheetData>
     <row r="1" spans="1:2" ht="107" customHeight="1">
       <c r="A1" s="41" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B1" s="41"/>
     </row>
     <row r="2" spans="1:2" ht="133" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="133" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="133" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="133" customHeight="1">
@@ -8559,15 +8559,15 @@
         <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="133" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="133" customHeight="1">
@@ -8575,7 +8575,7 @@
         <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="133" customHeight="1">
@@ -8583,7 +8583,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="133" customHeight="1">
@@ -8591,7 +8591,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="133" customHeight="1">
@@ -8599,7 +8599,7 @@
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="133" customHeight="1">
@@ -8607,7 +8607,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="133" customHeight="1">
@@ -8615,39 +8615,39 @@
         <v>26</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="16">
       <c r="A13" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="16">
       <c r="A14" s="4" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="71" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="71" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="109" customHeight="1">
@@ -8655,7 +8655,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="109" customHeight="1">
@@ -8663,15 +8663,15 @@
         <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="76" customHeight="1">
       <c r="A19" s="7" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -8696,771 +8696,771 @@
   <sheetData>
     <row r="1" spans="1:14" ht="98">
       <c r="A1" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>350</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="D1" s="12" t="s">
         <v>352</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="E1" s="12" t="s">
+        <v>835</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>354</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="H1" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>836</v>
+      </c>
+      <c r="L1" s="12" t="s">
         <v>837</v>
       </c>
-      <c r="F1" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="I1" s="12" t="s">
+      <c r="M1" s="14" t="s">
         <v>358</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="N1" s="12" t="s">
         <v>359</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>838</v>
-      </c>
-      <c r="L1" s="12" t="s">
-        <v>839</v>
-      </c>
-      <c r="M1" s="14" t="s">
-        <v>360</v>
-      </c>
-      <c r="N1" s="12" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="156">
       <c r="A2" s="15" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>159</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="H2" s="16" t="s">
         <v>365</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="I2" s="16" t="s">
         <v>366</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="J2" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="K2" s="17" t="s">
         <v>368</v>
-      </c>
-      <c r="J2" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>370</v>
       </c>
       <c r="L2" s="16"/>
       <c r="M2" s="14" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="N2" s="16" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="60">
       <c r="A3" s="15" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="D3" s="16" t="s">
         <v>374</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>375</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>376</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="H3" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="I3" s="16" t="s">
         <v>378</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>379</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="K3" s="17" t="s">
         <v>380</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>381</v>
-      </c>
-      <c r="K3" s="17" t="s">
-        <v>382</v>
       </c>
       <c r="L3" s="16"/>
       <c r="M3" s="14" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="48">
       <c r="A4" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>385</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="D4" s="16" t="s">
         <v>386</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>387</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>388</v>
       </c>
       <c r="E4" s="16"/>
       <c r="F4" s="16" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G4" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="I4" s="16" t="s">
         <v>389</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="J4" s="16" t="s">
         <v>390</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="K4" s="17" t="s">
         <v>391</v>
-      </c>
-      <c r="J4" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="K4" s="17" t="s">
-        <v>393</v>
       </c>
       <c r="L4" s="16"/>
       <c r="M4" s="14" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N4" s="16" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="182">
       <c r="A5" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>788</v>
+      </c>
+      <c r="C5" s="16" t="s">
         <v>789</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="D5" s="18" t="s">
         <v>790</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>791</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>792</v>
       </c>
       <c r="E5" s="16"/>
       <c r="F5" s="16" t="s">
+        <v>791</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>792</v>
+      </c>
+      <c r="I5" s="16" t="s">
         <v>793</v>
       </c>
-      <c r="G5" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="H5" s="16" t="s">
+      <c r="J5" s="16" t="s">
         <v>794</v>
       </c>
-      <c r="I5" s="16" t="s">
+      <c r="K5" s="17" t="s">
         <v>795</v>
-      </c>
-      <c r="J5" s="16" t="s">
-        <v>796</v>
-      </c>
-      <c r="K5" s="17" t="s">
-        <v>797</v>
       </c>
       <c r="L5" s="16"/>
       <c r="M5" s="14" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="N5" s="16" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="84">
       <c r="A6" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>396</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="D6" s="16" t="s">
         <v>397</v>
-      </c>
-      <c r="C6" s="16" t="s">
-        <v>398</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>399</v>
       </c>
       <c r="E6" s="16"/>
       <c r="F6" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="I6" s="16" t="s">
         <v>401</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="J6" s="16" t="s">
         <v>402</v>
       </c>
-      <c r="I6" s="16" t="s">
+      <c r="K6" s="17" t="s">
         <v>403</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>404</v>
-      </c>
-      <c r="K6" s="17" t="s">
-        <v>405</v>
       </c>
       <c r="L6" s="16"/>
       <c r="M6" s="14" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="N6" s="16" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="156">
       <c r="A7" s="15" t="s">
+        <v>406</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="C7" s="16" t="s">
         <v>408</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="D7" s="16" t="s">
         <v>409</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>410</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>411</v>
       </c>
       <c r="E7" s="16"/>
       <c r="F7" s="16" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G7" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="I7" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="J7" s="16" t="s">
         <v>413</v>
       </c>
-      <c r="I7" s="16" t="s">
+      <c r="K7" s="17" t="s">
         <v>414</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>415</v>
-      </c>
-      <c r="K7" s="17" t="s">
-        <v>416</v>
       </c>
       <c r="L7" s="16"/>
       <c r="M7" s="14" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="N7" s="16" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="72">
       <c r="A8" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="16" t="s">
         <v>419</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="D8" s="16" t="s">
         <v>420</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>421</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>422</v>
       </c>
       <c r="E8" s="16"/>
       <c r="F8" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="I8" s="16" t="s">
         <v>423</v>
       </c>
-      <c r="G8" s="16" t="s">
-        <v>389</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="J8" s="16" t="s">
         <v>424</v>
       </c>
-      <c r="I8" s="16" t="s">
+      <c r="K8" s="17" t="s">
         <v>425</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="K8" s="17" t="s">
-        <v>427</v>
       </c>
       <c r="L8" s="16"/>
       <c r="M8" s="14" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="N8" s="16" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="156">
       <c r="A9" s="15" t="s">
+        <v>428</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>430</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="D9" s="16" t="s">
         <v>431</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>432</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>433</v>
       </c>
       <c r="E9" s="16"/>
       <c r="F9" s="16"/>
       <c r="G9" s="16" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="H9" s="16"/>
       <c r="I9" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="K9" s="17" t="s">
         <v>435</v>
       </c>
-      <c r="J9" s="16" t="s">
+      <c r="L9" s="16" t="s">
         <v>436</v>
       </c>
-      <c r="K9" s="17" t="s">
+      <c r="M9" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="N9" s="16" t="s">
         <v>438</v>
-      </c>
-      <c r="M9" s="14" t="s">
-        <v>439</v>
-      </c>
-      <c r="N9" s="16" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="144">
       <c r="A10" s="15" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E10" s="16"/>
       <c r="F10" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G10" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>802</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>803</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="J10" s="16" t="s">
         <v>804</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="K10" s="19" t="s">
         <v>805</v>
-      </c>
-      <c r="J10" s="16" t="s">
-        <v>806</v>
-      </c>
-      <c r="K10" s="19" t="s">
-        <v>807</v>
       </c>
       <c r="L10" s="16"/>
       <c r="M10" s="14" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="N10" s="16" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="108">
       <c r="A11" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>441</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="D11" s="16" t="s">
         <v>442</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>443</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>444</v>
       </c>
       <c r="E11" s="16"/>
       <c r="F11" s="16"/>
       <c r="G11" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="I11" s="16"/>
       <c r="J11" s="16" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="L11" s="16"/>
       <c r="M11" s="14" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="N11" s="16" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="120">
       <c r="A12" s="15" t="s">
+        <v>448</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>450</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>451</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>452</v>
-      </c>
       <c r="D12" s="16" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="E12" s="16"/>
       <c r="F12" s="16"/>
       <c r="G12" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H12" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="J12" s="16" t="s">
         <v>453</v>
       </c>
-      <c r="I12" s="16" t="s">
+      <c r="K12" s="17" t="s">
         <v>454</v>
-      </c>
-      <c r="J12" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>456</v>
       </c>
       <c r="L12" s="16"/>
       <c r="M12" s="14" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="84">
       <c r="A13" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="D13" s="16" t="s">
         <v>460</v>
-      </c>
-      <c r="C13" s="16" t="s">
-        <v>461</v>
-      </c>
-      <c r="D13" s="16" t="s">
-        <v>462</v>
       </c>
       <c r="E13" s="16"/>
       <c r="F13" s="16" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H13" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="J13" s="16" t="s">
         <v>463</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="K13" s="17" t="s">
         <v>464</v>
-      </c>
-      <c r="J13" s="16" t="s">
-        <v>465</v>
-      </c>
-      <c r="K13" s="17" t="s">
-        <v>466</v>
       </c>
       <c r="L13" s="16"/>
       <c r="M13" s="14" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N13" s="16" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="96">
       <c r="A14" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>469</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="D14" s="16" t="s">
         <v>470</v>
-      </c>
-      <c r="C14" s="16" t="s">
-        <v>471</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>472</v>
       </c>
       <c r="E14" s="16"/>
       <c r="F14" s="16"/>
       <c r="G14" s="16" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16"/>
       <c r="J14" s="16" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="L14" s="16"/>
       <c r="M14" s="20"/>
       <c r="N14" s="16" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="84">
       <c r="A15" s="15" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>477</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="D15" s="16" t="s">
         <v>478</v>
-      </c>
-      <c r="C15" s="16" t="s">
-        <v>479</v>
-      </c>
-      <c r="D15" s="16" t="s">
-        <v>480</v>
       </c>
       <c r="E15" s="16"/>
       <c r="F15" s="16"/>
       <c r="G15" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>480</v>
+      </c>
+      <c r="I15" s="16" t="s">
         <v>481</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="J15" s="16" t="s">
         <v>482</v>
       </c>
-      <c r="I15" s="16" t="s">
+      <c r="K15" s="17" t="s">
         <v>483</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="K15" s="17" t="s">
-        <v>485</v>
       </c>
       <c r="L15" s="16"/>
       <c r="M15" s="14" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="72">
       <c r="A16" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>487</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="D16" s="16" t="s">
         <v>488</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>490</v>
       </c>
       <c r="E16" s="16"/>
       <c r="F16" s="16" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="G16" s="16" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H16" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="J16" s="16" t="s">
         <v>491</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="K16" s="17" t="s">
         <v>492</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>493</v>
-      </c>
-      <c r="K16" s="17" t="s">
-        <v>494</v>
       </c>
       <c r="L16" s="16"/>
       <c r="M16" s="14" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="N16" s="16" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="72">
       <c r="A17" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="D17" s="16" t="s">
         <v>498</v>
-      </c>
-      <c r="C17" s="16" t="s">
-        <v>499</v>
-      </c>
-      <c r="D17" s="16" t="s">
-        <v>500</v>
       </c>
       <c r="E17" s="16"/>
       <c r="F17" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>500</v>
+      </c>
+      <c r="I17" s="16" t="s">
         <v>501</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="H17" s="16" t="s">
+      <c r="J17" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="I17" s="16" t="s">
+      <c r="K17" s="17" t="s">
         <v>503</v>
-      </c>
-      <c r="J17" s="16" t="s">
-        <v>504</v>
-      </c>
-      <c r="K17" s="17" t="s">
-        <v>505</v>
       </c>
       <c r="L17" s="16"/>
       <c r="M17" s="14" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="N17" s="16" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="204">
       <c r="A18" s="15" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B18" s="16" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="E18" s="16"/>
       <c r="F18" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G18" s="16" t="s">
+        <v>509</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="I18" s="16" t="s">
         <v>511</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="J18" s="16" t="s">
         <v>512</v>
       </c>
-      <c r="I18" s="16" t="s">
+      <c r="K18" s="17" t="s">
         <v>513</v>
-      </c>
-      <c r="J18" s="16" t="s">
-        <v>514</v>
-      </c>
-      <c r="K18" s="17" t="s">
-        <v>515</v>
       </c>
       <c r="L18" s="16"/>
       <c r="M18" s="14" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="42">
       <c r="A19" s="15" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B19" s="16" t="s">
         <v>173</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E19" s="16"/>
       <c r="F19" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G19" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>519</v>
+      </c>
+      <c r="I19" s="16" t="s">
         <v>520</v>
-      </c>
-      <c r="H19" s="16" t="s">
-        <v>521</v>
-      </c>
-      <c r="I19" s="16" t="s">
-        <v>522</v>
       </c>
       <c r="J19" s="16"/>
       <c r="K19" s="17"/>
       <c r="L19" s="16"/>
       <c r="M19" s="14" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="28">
       <c r="A20" s="15" t="s">
+        <v>523</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="D20" s="16" t="s">
         <v>526</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>527</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>528</v>
       </c>
       <c r="E20" s="16"/>
       <c r="F20" s="16" t="s">
+        <v>527</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>528</v>
+      </c>
+      <c r="H20" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="I20" s="16" t="s">
         <v>530</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>531</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>532</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>203</v>
@@ -9470,286 +9470,286 @@
       </c>
       <c r="L20" s="16"/>
       <c r="M20" s="14" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="156">
       <c r="A21" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="D21" s="16" t="s">
         <v>536</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>537</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>538</v>
       </c>
       <c r="E21" s="16"/>
       <c r="F21" s="16" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G21" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="I21" s="16" t="s">
         <v>539</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="J21" s="16" t="s">
+        <v>811</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="L21" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="I21" s="16" t="s">
+      <c r="M21" s="14" t="s">
         <v>541</v>
       </c>
-      <c r="J21" s="16" t="s">
-        <v>813</v>
-      </c>
-      <c r="K21" s="17" t="s">
-        <v>814</v>
-      </c>
-      <c r="L21" s="16" t="s">
+      <c r="N21" s="16" t="s">
         <v>542</v>
-      </c>
-      <c r="M21" s="14" t="s">
-        <v>543</v>
-      </c>
-      <c r="N21" s="16" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="48">
       <c r="A22" s="15" t="s">
+        <v>543</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>545</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="D22" s="16" t="s">
         <v>546</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>548</v>
       </c>
       <c r="E22" s="16"/>
       <c r="F22" s="16" t="s">
+        <v>547</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="I22" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="G22" s="16" t="s">
-        <v>401</v>
-      </c>
-      <c r="H22" s="16" t="s">
+      <c r="J22" s="16" t="s">
         <v>550</v>
       </c>
-      <c r="I22" s="16" t="s">
+      <c r="K22" s="17" t="s">
         <v>551</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>552</v>
-      </c>
-      <c r="K22" s="17" t="s">
-        <v>553</v>
       </c>
       <c r="L22" s="16"/>
       <c r="M22" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="N22" s="16" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="168">
       <c r="A23" s="21" t="s">
+        <v>813</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>815</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="D23" s="16" t="s">
         <v>816</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>817</v>
-      </c>
-      <c r="D23" s="16" t="s">
-        <v>818</v>
       </c>
       <c r="E23" s="16"/>
       <c r="F23" s="16" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H23" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="J23" s="22" t="s">
         <v>819</v>
       </c>
-      <c r="I23" s="16" t="s">
+      <c r="K23" s="17" t="s">
         <v>820</v>
-      </c>
-      <c r="J23" s="22" t="s">
-        <v>821</v>
-      </c>
-      <c r="K23" s="17" t="s">
-        <v>822</v>
       </c>
       <c r="L23" s="16"/>
       <c r="M23" s="14" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="N23" s="16" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="42">
       <c r="A24" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="C24" s="16" t="s">
         <v>556</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="D24" s="16" t="s">
         <v>557</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>558</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>559</v>
       </c>
       <c r="E24" s="16"/>
       <c r="F24" s="16" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H24" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="J24" s="16" t="s">
         <v>560</v>
       </c>
-      <c r="I24" s="16" t="s">
+      <c r="K24" s="17" t="s">
         <v>561</v>
-      </c>
-      <c r="J24" s="16" t="s">
-        <v>562</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>563</v>
       </c>
       <c r="L24" s="16"/>
       <c r="M24" s="14" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="N24" s="16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="60">
       <c r="A25" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="C25" s="16" t="s">
         <v>566</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="D25" s="16" t="s">
         <v>567</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>568</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>569</v>
       </c>
       <c r="E25" s="16"/>
       <c r="F25" s="16"/>
       <c r="G25" s="16" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I25" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="K25" s="17" t="s">
         <v>570</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>571</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>572</v>
       </c>
       <c r="L25" s="16"/>
       <c r="M25" s="20" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="N25" s="16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="96">
       <c r="A26" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="B26" s="24" t="s">
+        <v>574</v>
+      </c>
+      <c r="C26" s="24" t="s">
         <v>575</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="D26" s="24" t="s">
         <v>576</v>
-      </c>
-      <c r="C26" s="24" t="s">
-        <v>577</v>
-      </c>
-      <c r="D26" s="24" t="s">
-        <v>578</v>
       </c>
       <c r="E26" s="24"/>
       <c r="F26" s="24"/>
       <c r="G26" s="24" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="H26" s="24" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="I26" s="24"/>
       <c r="J26" s="24" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="K26" s="25" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="L26" s="24"/>
       <c r="M26" s="14" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="N26" s="24" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="124">
       <c r="A27" s="26" t="s">
+        <v>824</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>825</v>
+      </c>
+      <c r="C27" s="26" t="s">
         <v>826</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="D27" s="26" t="s">
         <v>827</v>
-      </c>
-      <c r="C27" s="26" t="s">
-        <v>828</v>
-      </c>
-      <c r="D27" s="26" t="s">
-        <v>829</v>
       </c>
       <c r="E27" s="26"/>
       <c r="F27" s="26" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G27" s="26" t="s">
+        <v>828</v>
+      </c>
+      <c r="H27" s="26" t="s">
+        <v>829</v>
+      </c>
+      <c r="I27" s="8" t="s">
         <v>830</v>
       </c>
-      <c r="H27" s="26" t="s">
+      <c r="J27" s="26" t="s">
         <v>831</v>
       </c>
-      <c r="I27" s="8" t="s">
+      <c r="K27" s="8" t="s">
         <v>832</v>
-      </c>
-      <c r="J27" s="26" t="s">
-        <v>833</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>834</v>
       </c>
       <c r="L27" s="26"/>
       <c r="M27" s="8" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="N27" s="26" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
     </row>
   </sheetData>
